--- a/Annotations/annotations_EN.xlsx
+++ b/Annotations/annotations_EN.xlsx
@@ -424,7 +424,7 @@
         <v>The accused will be released if they innocent</v>
       </c>
       <c r="D2" t="str">
-        <v>Neutral</v>
+        <v>NonSense</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>They will only build for Fermilab.</v>
       </c>
       <c r="D3" t="str">
-        <v>Neutral</v>
+        <v>NonSense</v>
       </c>
     </row>
     <row r="4">
@@ -452,7 +452,7 @@
         <v>If you take the year Robin Rimbaud was born in and reverse the digits, you would get 4691.</v>
       </c>
       <c r="D4" t="str">
-        <v>Neutral</v>
+        <v>NonSense</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         <v>The most common home bug bite is a red bug bite.</v>
       </c>
       <c r="D5" t="str">
-        <v>Neutral</v>
+        <v>NonSense</v>
       </c>
     </row>
     <row r="6">

--- a/Annotations/annotations_EN.xlsx
+++ b/Annotations/annotations_EN.xlsx
@@ -424,7 +424,7 @@
         <v>The accused will be released if they innocent</v>
       </c>
       <c r="D2" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>They will only build for Fermilab.</v>
       </c>
       <c r="D3" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="4">
@@ -452,7 +452,7 @@
         <v>If you take the year Robin Rimbaud was born in and reverse the digits, you would get 4691.</v>
       </c>
       <c r="D4" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         <v>The most common home bug bite is a red bug bite.</v>
       </c>
       <c r="D5" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="6">
@@ -494,7 +494,7 @@
         <v>The Necessary and Proper Clause applies particularly to expired copyrights.</v>
       </c>
       <c r="D7" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="8">
@@ -508,7 +508,7 @@
         <v>Eveland is from the township of Orange County.</v>
       </c>
       <c r="D8" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         <v>Senator Ghitter is going to run for president.</v>
       </c>
       <c r="D9" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         <v>the east texas man and woman are of sound mind</v>
       </c>
       <c r="D10" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="11">
@@ -550,7 +550,7 @@
         <v>The meeting was held October 1 1998.</v>
       </c>
       <c r="D11" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="12">
@@ -564,7 +564,7 @@
         <v>Threats were made at a certain time in history regarding the uncertainty of particular sanctions being implemented. These sanctions would make an entity extremely upset.</v>
       </c>
       <c r="D12" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
         <v>A program can run on the corresponding Fermi Linux LTS release if it is not RedHat Enterprise certified.</v>
       </c>
       <c r="D13" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="14">
@@ -592,7 +592,7 @@
         <v>If you never use the area, it will be enough with a couple of times a week</v>
       </c>
       <c r="D14" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="15">
@@ -606,7 +606,7 @@
         <v>The home was completed in the 1940s.</v>
       </c>
       <c r="D15" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="16">
@@ -620,7 +620,7 @@
         <v>The "they" referenced in this context have sided completely with the prosecution.</v>
       </c>
       <c r="D16" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="17">
@@ -634,7 +634,7 @@
         <v>The article says to use up the majority of the gas in the car.</v>
       </c>
       <c r="D17" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="18">
@@ -648,7 +648,7 @@
         <v>The two men are in prison for 20 years.</v>
       </c>
       <c r="D18" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="19">
@@ -662,7 +662,7 @@
         <v>Its helpful to know if your opponent has had too much to drink</v>
       </c>
       <c r="D19" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="20">
@@ -676,7 +676,7 @@
         <v>Michael Jackson is dead</v>
       </c>
       <c r="D20" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="21">
@@ -690,7 +690,7 @@
         <v>No emphasis has been put on early learning</v>
       </c>
       <c r="D21" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="22">
@@ -704,7 +704,7 @@
         <v>Get off at the national folk park stop and walk from there to the main entrance.</v>
       </c>
       <c r="D22" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="23">
@@ -718,7 +718,7 @@
         <v>The shooting lasted until Tuesday morning</v>
       </c>
       <c r="D23" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="24">
@@ -732,7 +732,7 @@
         <v xml:space="preserve">The reform was meant to harmonize spelling rules. </v>
       </c>
       <c r="D24" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="25">
@@ -746,7 +746,7 @@
         <v>How your hose looks will tell you how it was damaged.</v>
       </c>
       <c r="D25" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="26">
@@ -760,7 +760,7 @@
         <v>People like sleeping in a cold room</v>
       </c>
       <c r="D26" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="27">
@@ -774,7 +774,7 @@
         <v>If you used to watch SportsCenter at 12pm on Wednesdays, there is a chance you know who Chris McKendry is.</v>
       </c>
       <c r="D27" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="28">
@@ -788,7 +788,7 @@
         <v>Being singled out if fair</v>
       </c>
       <c r="D28" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="29">
@@ -802,7 +802,7 @@
         <v>The agent was part of the military</v>
       </c>
       <c r="D29" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="30">
@@ -816,7 +816,7 @@
         <v>Anyone can grow african violets if they just have the willpower.</v>
       </c>
       <c r="D30" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="31">
@@ -830,7 +830,7 @@
         <v>Only go to sleep when its cool</v>
       </c>
       <c r="D31" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="32">
@@ -844,7 +844,7 @@
         <v>Lasting peace will be achieved</v>
       </c>
       <c r="D32" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         <v>Daylights savings time will affect your practice, take it into account.</v>
       </c>
       <c r="D33" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="34">
@@ -872,7 +872,7 @@
         <v>Adults can have adhd.</v>
       </c>
       <c r="D34" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="35">
@@ -886,7 +886,7 @@
         <v>Bill C-3 provides an exemption that authorizes judges to take samples.</v>
       </c>
       <c r="D35" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="36">
@@ -900,7 +900,7 @@
         <v>If you stop smoking tobacco products, you will not get lung cancer.</v>
       </c>
       <c r="D36" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="37">
@@ -914,7 +914,7 @@
         <v>Employees were reluctant to give affidavigts.</v>
       </c>
       <c r="D37" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="38">
@@ -928,7 +928,7 @@
         <v>Dalai Lama is a peace loving leader</v>
       </c>
       <c r="D38" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="39">
@@ -942,7 +942,7 @@
         <v xml:space="preserve">Jongno has a fleet of buses </v>
       </c>
       <c r="D39" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="40">
@@ -956,7 +956,7 @@
         <v>This person studies copyright law</v>
       </c>
       <c r="D40" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="41">
@@ -970,7 +970,7 @@
         <v>Don't take vitamin E.</v>
       </c>
       <c r="D41" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="42">
@@ -984,7 +984,7 @@
         <v>Europeans change copyright details</v>
       </c>
       <c r="D42" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="43">
@@ -998,7 +998,7 @@
         <v>Mixbin Electronics makes electronics</v>
       </c>
       <c r="D43" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="44">
@@ -1012,7 +1012,7 @@
         <v>Medicine has came along way since it first started in the America's.</v>
       </c>
       <c r="D44" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="45">
@@ -1026,7 +1026,7 @@
         <v>The statement names people whos names start with an M and a F</v>
       </c>
       <c r="D45" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="46">
@@ -1054,7 +1054,7 @@
         <v>Your heart control's your body's clock.</v>
       </c>
       <c r="D47" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="48">
@@ -1068,7 +1068,7 @@
         <v>there is another paragraph</v>
       </c>
       <c r="D48" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="49">
@@ -1082,7 +1082,7 @@
         <v>If smoking causes abnormal cells, then abnormal cells are the sole cause of cancer.</v>
       </c>
       <c r="D49" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="50">
@@ -1096,7 +1096,7 @@
         <v xml:space="preserve">North Korea has installed new inspection cameras. </v>
       </c>
       <c r="D50" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="51">
@@ -1110,7 +1110,7 @@
         <v>you can win if the opponent is alone.</v>
       </c>
       <c r="D51" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="52">
@@ -1124,7 +1124,7 @@
         <v>Selling a car is like selling water in a desert</v>
       </c>
       <c r="D52" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="53">
@@ -1138,7 +1138,7 @@
         <v>Buckingham usually spoke at meetings.</v>
       </c>
       <c r="D53" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="54">
@@ -1152,7 +1152,7 @@
         <v>Mopping is necessary for this type of tile</v>
       </c>
       <c r="D54" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="55">
@@ -1166,7 +1166,7 @@
         <v>Doctors will keep track of a patient's vaccination history</v>
       </c>
       <c r="D55" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="56">
@@ -1180,7 +1180,7 @@
         <v>The question is hard to answer</v>
       </c>
       <c r="D56" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="57">
@@ -1194,7 +1194,7 @@
         <v>copyright laws have been around over 200 years</v>
       </c>
       <c r="D57" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="58">
@@ -1208,7 +1208,7 @@
         <v>This important letter is in regard to the comments made by Beth Eveland</v>
       </c>
       <c r="D58" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="59">
@@ -1222,7 +1222,7 @@
         <v>Haloumi cheese is best to eat outside</v>
       </c>
       <c r="D59" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="60">
@@ -1236,7 +1236,7 @@
         <v>Belgium is mostly Flemish.</v>
       </c>
       <c r="D60" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="61">
@@ -1250,7 +1250,7 @@
         <v>Lyme disease is genetic.</v>
       </c>
       <c r="D61" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="62">
@@ -1264,7 +1264,7 @@
         <v>Austria is a film.</v>
       </c>
       <c r="D62" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="63">
@@ -1278,7 +1278,7 @@
         <v>Rich Girl features a German rapper.</v>
       </c>
       <c r="D63" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="64">
@@ -1292,7 +1292,7 @@
         <v>Louis Tomlinson appeared in an ITV comedy.</v>
       </c>
       <c r="D64" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="65">
@@ -1306,7 +1306,7 @@
         <v>Jennifer Garner was in a movie.</v>
       </c>
       <c r="D65" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="66">
@@ -1320,7 +1320,7 @@
         <v>James Wilson is a real person yet to be made into a fictional character.</v>
       </c>
       <c r="D66" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="67">
@@ -1334,7 +1334,7 @@
         <v>Mr. Michael will be prosecuted.</v>
       </c>
       <c r="D67" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="68">
@@ -1348,7 +1348,7 @@
         <v>One would feel slighted if they received an invitation to a bris.</v>
       </c>
       <c r="D68" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="69">
@@ -1362,7 +1362,7 @@
         <v>The channel has since been removed for download from the internet.</v>
       </c>
       <c r="D69" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="70">
@@ -1376,7 +1376,7 @@
         <v>A prerequisite for downloading the channel is having Internet Explorer installed.</v>
       </c>
       <c r="D70" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="71">
@@ -1390,7 +1390,7 @@
         <v>There is a set number of voters.</v>
       </c>
       <c r="D71" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="72">
@@ -1404,7 +1404,7 @@
         <v>Options traders slapped the palms of their hands together in applause for Scholes and Merton</v>
       </c>
       <c r="D72" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="73">
@@ -1418,7 +1418,7 @@
         <v>If we don't pay attention to the MacDonalds of the world, they will just go away on their own.</v>
       </c>
       <c r="D73" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="74">
@@ -1432,7 +1432,7 @@
         <v>It's a very positive sign that 20% of new mutual fund money is going into indexed funds.</v>
       </c>
       <c r="D74" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="75">
@@ -1446,7 +1446,7 @@
         <v>Andrew Baumgartner is a boring teacher</v>
       </c>
       <c r="D75" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="76">
@@ -1460,7 +1460,7 @@
         <v>The big boys thought it was risk free.</v>
       </c>
       <c r="D76" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="77">
@@ -1474,7 +1474,7 @@
         <v>The survey is available for taking online.</v>
       </c>
       <c r="D77" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="78">
@@ -1488,7 +1488,7 @@
         <v>The Pro-choice media is willing to except stats that support their claim, even if they're incorrect.</v>
       </c>
       <c r="D78" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="79">
@@ -1502,7 +1502,7 @@
         <v>Jerry Seinfeld makes quite charming seem a tad immature.</v>
       </c>
       <c r="D79" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="80">
@@ -1516,7 +1516,7 @@
         <v>Kennewick Man has a choice to make himself about his reservation if evidence is existent.</v>
       </c>
       <c r="D80" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="81">
@@ -1530,7 +1530,7 @@
         <v>Often one hears applause on the options exchange floor.</v>
       </c>
       <c r="D81" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="82">
@@ -1544,7 +1544,7 @@
         <v>As it turns out, Lewinsky and Tripp would become good friends if Clinton expressed his sorrow and remorse.</v>
       </c>
       <c r="D82" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="83">
@@ -1558,7 +1558,7 @@
         <v>There is a cultural civil war going on.</v>
       </c>
       <c r="D83" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="84">
@@ -1586,7 +1586,7 @@
         <v>Advertisers would abandon the periodical if it were free</v>
       </c>
       <c r="D85" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="86">
@@ -1600,7 +1600,7 @@
         <v>He stands to lose a lot more if he buys at a margin.</v>
       </c>
       <c r="D86" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="87">
@@ -1614,7 +1614,7 @@
         <v>Sheen is on a path that leads to death.</v>
       </c>
       <c r="D87" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="88">
@@ -1628,7 +1628,7 @@
         <v>After successfully domesticating animals, it's a personal choice to use them as pets</v>
       </c>
       <c r="D88" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="89">
@@ -1642,7 +1642,7 @@
         <v>You can click here to read Jon Robin Baitz's take on the controversy and his opinion on censorship.</v>
       </c>
       <c r="D89" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="90">
@@ -1656,7 +1656,7 @@
         <v>What if there was another player?</v>
       </c>
       <c r="D90" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="91">
@@ -1670,7 +1670,7 @@
         <v>Landsburg is criticizing the United States of America.</v>
       </c>
       <c r="D91" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="92">
@@ -1684,7 +1684,7 @@
         <v>Few, if any physical publications are pricey - for the most part, they are very affordable.</v>
       </c>
       <c r="D92" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="93">
@@ -1698,7 +1698,7 @@
         <v>The abortion procedure matters</v>
       </c>
       <c r="D93" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="94">
@@ -1712,7 +1712,7 @@
         <v>Using the IRA account before retiring can produce tax benefits</v>
       </c>
       <c r="D94" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="95">
@@ -1726,7 +1726,7 @@
         <v>A subtle approach for their exit is acceptable</v>
       </c>
       <c r="D95" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="96">
@@ -1740,7 +1740,7 @@
         <v>There are congressmen who have ridden the New York City subway.</v>
       </c>
       <c r="D96" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="97">
@@ -1754,7 +1754,7 @@
         <v>Isikoff's journalism has brought him disdain from others.</v>
       </c>
       <c r="D97" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="98">
@@ -1768,7 +1768,7 @@
         <v>Bill Gates struggles to pay his bills.</v>
       </c>
       <c r="D98" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="99">
@@ -1782,7 +1782,7 @@
         <v>Critics are dismissive of all social novels.</v>
       </c>
       <c r="D99" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="100">
@@ -1796,7 +1796,7 @@
         <v>Dining on Crustaceans make you seem like you eat in a birdlike manner.</v>
       </c>
       <c r="D100" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="101">
@@ -1810,7 +1810,7 @@
         <v>The report in Dallas Morning News helped to shed more light into the event that took place between Clinton and Lewinsky.</v>
       </c>
       <c r="D101" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="102">
@@ -1824,7 +1824,7 @@
         <v>He consented because the alternative was impeachment.</v>
       </c>
       <c r="D102" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="103">
@@ -1838,7 +1838,7 @@
         <v>George Bush Sr.'s and George W Bush are both from the south</v>
       </c>
       <c r="D103" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="104">
@@ -1852,7 +1852,7 @@
         <v>Most of the negatives reappeared.</v>
       </c>
       <c r="D104" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="105">
@@ -1866,7 +1866,7 @@
         <v>Abortion is unpleasant.</v>
       </c>
       <c r="D105" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="106">
@@ -1880,7 +1880,7 @@
         <v>Some people care if the judges are honest.</v>
       </c>
       <c r="D106" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="107">
@@ -1894,7 +1894,7 @@
         <v>Partial-birth abortions, D and Es are all the same.</v>
       </c>
       <c r="D107" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="108">
@@ -1908,7 +1908,7 @@
         <v>The couple are making a gay video, they had never met beforehand.</v>
       </c>
       <c r="D108" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="109">
@@ -1922,7 +1922,7 @@
         <v>It looked like it was going to fail.</v>
       </c>
       <c r="D109" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="110">
@@ -1936,7 +1936,7 @@
         <v>The refresher course is mandatory</v>
       </c>
       <c r="D110" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="111">
@@ -1950,7 +1950,7 @@
         <v>the reason is within the answer.</v>
       </c>
       <c r="D111" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="112">
@@ -1964,7 +1964,7 @@
         <v>No violence in ordinary drams is wrong.</v>
       </c>
       <c r="D112" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="113">
@@ -1978,7 +1978,7 @@
         <v>The Mediaphiles are seen as a new era.</v>
       </c>
       <c r="D113" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="114">
@@ -1992,7 +1992,7 @@
         <v>They were definitely going to buy it.</v>
       </c>
       <c r="D114" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="115">
@@ -2006,7 +2006,7 @@
         <v>Wall Street and the Mediaphiles have a lot in common.</v>
       </c>
       <c r="D115" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="116">
@@ -2020,7 +2020,7 @@
         <v>The absence of patients suing insurers would be a step in the right direction.</v>
       </c>
       <c r="D116" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="117">
@@ -2034,7 +2034,7 @@
         <v>He intends to become a serious threat</v>
       </c>
       <c r="D117" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="118">
@@ -2048,7 +2048,7 @@
         <v>The story is hilarious.</v>
       </c>
       <c r="D118" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="119">
@@ -2062,7 +2062,7 @@
         <v>The government does not control embargos</v>
       </c>
       <c r="D119" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="120">
@@ -2076,7 +2076,7 @@
         <v xml:space="preserve">If you have a kid who is already covered by insurance then the program will not cover them. </v>
       </c>
       <c r="D120" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="121">
@@ -2090,7 +2090,7 @@
         <v>No one will conclude that it is a masterpiece on their own accord.</v>
       </c>
       <c r="D121" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="122">
@@ -2104,7 +2104,7 @@
         <v>if only there were severe consequences from the law</v>
       </c>
       <c r="D122" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="123">
@@ -2118,7 +2118,7 @@
         <v>The Y-intercepts would remain unchanged overall even if the vertical axis had a change in data.</v>
       </c>
       <c r="D123" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="124">
@@ -2132,7 +2132,7 @@
         <v>Conservatives say perjury is perjury and no one can get away with it.</v>
       </c>
       <c r="D124" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="125">
@@ -2146,7 +2146,7 @@
         <v>He found a person willing to work those hours after two months of searching.</v>
       </c>
       <c r="D125" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="126">
@@ -2160,7 +2160,7 @@
         <v>The change will offer it's own protection.</v>
       </c>
       <c r="D126" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="127">
@@ -2174,7 +2174,7 @@
         <v xml:space="preserve">Cycling in the French metropolitan area is safe and relaxing. </v>
       </c>
       <c r="D127" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="128">
@@ -2188,7 +2188,7 @@
         <v xml:space="preserve">It is unclear if abuse is occurring more often, or simply being reported more often. </v>
       </c>
       <c r="D128" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="129">
@@ -2202,7 +2202,7 @@
         <v>An intern doesn't get paid.</v>
       </c>
       <c r="D129" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="130">
@@ -2216,7 +2216,7 @@
         <v>He's not a good friend if he tells you you'll love Happy Texas, wrote the article.</v>
       </c>
       <c r="D130" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="131">
@@ -2230,7 +2230,7 @@
         <v>I will go once in a while when I feel like it.</v>
       </c>
       <c r="D131" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="132">
@@ -2244,7 +2244,7 @@
         <v>Even if you charge money, complying with the rules can be possible.</v>
       </c>
       <c r="D132" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="133">
@@ -2258,7 +2258,7 @@
         <v>If it wasn't Turkey</v>
       </c>
       <c r="D133" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="134">
@@ -2272,7 +2272,7 @@
         <v>It is hard to tell at first if Fred is good.</v>
       </c>
       <c r="D134" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="135">
@@ -2286,7 +2286,7 @@
         <v>The clerk said that if I choose to engrave, he'll give me a 20% discount.</v>
       </c>
       <c r="D135" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="136">
@@ -2300,7 +2300,7 @@
         <v>If the band shouts ole, it means the matador is doing badly.</v>
       </c>
       <c r="D136" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="137">
@@ -2314,7 +2314,7 @@
         <v>What we did to Natives makes Custer look kind.</v>
       </c>
       <c r="D137" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="138">
@@ -2328,7 +2328,7 @@
         <v>Many people like to buy a stuffed puffer fish as a souvenir that doubles as a lamp shade.</v>
       </c>
       <c r="D138" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="139">
@@ -2342,7 +2342,7 @@
         <v xml:space="preserve">That's not the problem </v>
       </c>
       <c r="D139" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="140">
@@ -2370,7 +2370,7 @@
         <v>He has access to all of the information and will act quickly if slighted.</v>
       </c>
       <c r="D141" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="142">
@@ -2384,7 +2384,7 @@
         <v>He would love it if we respected his legacy.</v>
       </c>
       <c r="D142" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="143">
@@ -2398,7 +2398,7 @@
         <v>Behind the opera house there's two of the best known department stores if you can find them</v>
       </c>
       <c r="D143" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="144">
@@ -2412,7 +2412,7 @@
         <v>You are aware you do not cast a vote for any candidate.</v>
       </c>
       <c r="D144" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="145">
@@ -2426,7 +2426,7 @@
         <v xml:space="preserve">Everyone gets help from parents for college. </v>
       </c>
       <c r="D145" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="146">
@@ -2440,7 +2440,7 @@
         <v>The links in the article contain different material than the links at the bottom of the article.</v>
       </c>
       <c r="D146" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="147">
@@ -2454,7 +2454,7 @@
         <v>The master shoemaker kept a professional relationship with his assistant.</v>
       </c>
       <c r="D147" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="148">
@@ -2468,7 +2468,7 @@
         <v xml:space="preserve">If you are lucky, it will not happen. </v>
       </c>
       <c r="D148" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="149">
@@ -2482,7 +2482,7 @@
         <v>If I were to be truthful, it won't always save your fingers.</v>
       </c>
       <c r="D149" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="150">
@@ -2496,7 +2496,7 @@
         <v>You are not required to consult with eh LSC if there are problems.</v>
       </c>
       <c r="D150" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="151">
@@ -2510,7 +2510,7 @@
         <v>I expect the results to be substantially different.</v>
       </c>
       <c r="D151" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="152">
@@ -2524,7 +2524,7 @@
         <v xml:space="preserve">Will we continue to be friends if I change? </v>
       </c>
       <c r="D152" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="153">
@@ -2538,7 +2538,7 @@
         <v>He was asked about photographers from California in particular.</v>
       </c>
       <c r="D153" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="154">
@@ -2552,7 +2552,7 @@
         <v>Having installations every five years or every three years does affect labor costs.</v>
       </c>
       <c r="D154" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="155">
@@ -2566,7 +2566,7 @@
         <v>The GOP has low voter turn out.</v>
       </c>
       <c r="D155" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="156">
@@ -2580,7 +2580,7 @@
         <v>How long do I wait for someone to remove their clothes from the washer or dryer?</v>
       </c>
       <c r="D156" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="157">
@@ -2594,7 +2594,7 @@
         <v>The judge pointed at the loud women and demanded immediate silence.</v>
       </c>
       <c r="D157" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="158">
@@ -2608,7 +2608,7 @@
         <v>It is known that you will understand their language by listening them sing.</v>
       </c>
       <c r="D158" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="159">
@@ -2622,7 +2622,7 @@
         <v>His grandmother's in a terrible state now.</v>
       </c>
       <c r="D159" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="160">
@@ -2636,7 +2636,7 @@
         <v>You win a free coffee if you send in this particular card.</v>
       </c>
       <c r="D160" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="161">
@@ -2650,7 +2650,7 @@
         <v>If we can see proof that those people are getting out of the country then those people are not going to stay.</v>
       </c>
       <c r="D161" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="162">
@@ -2664,7 +2664,7 @@
         <v>Though it was a long time ago, it still really does matter.</v>
       </c>
       <c r="D162" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="163">
@@ -2678,7 +2678,7 @@
         <v xml:space="preserve">Some wonder if Clinton will plead the fith if summoned to court. </v>
       </c>
       <c r="D163" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="164">
@@ -2692,7 +2692,7 @@
         <v>It is a hike to get to the Victoria Peak Gardens.</v>
       </c>
       <c r="D164" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="165">
@@ -2706,7 +2706,7 @@
         <v>If you don't use it before the end of the year it's gone.</v>
       </c>
       <c r="D165" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="166">
@@ -2720,7 +2720,7 @@
         <v>Publishing in trauma and emergency journals are the only way of changing practices.</v>
       </c>
       <c r="D166" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="167">
@@ -2734,7 +2734,7 @@
         <v>Seller do not always have sufficient physical presence in a state.</v>
       </c>
       <c r="D167" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="168">
@@ -2748,7 +2748,7 @@
         <v>The narrator is a vampire and this is one of their vampire powers.</v>
       </c>
       <c r="D168" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="169">
@@ -2776,7 +2776,7 @@
         <v>It is a weird car called the Saab, unsure if it exists down there.</v>
       </c>
       <c r="D170" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="171">
@@ -2790,7 +2790,7 @@
         <v>There's not a single reason why any government would embargo this product.</v>
       </c>
       <c r="D171" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="172">
@@ -2804,7 +2804,7 @@
         <v>Did you not understand how credit works?</v>
       </c>
       <c r="D172" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="173">
@@ -2818,7 +2818,7 @@
         <v xml:space="preserve">We haven't had any billing experience with the company. </v>
       </c>
       <c r="D173" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="174">
@@ -2832,7 +2832,7 @@
         <v>It's sure that no communication corresponds to no lies.</v>
       </c>
       <c r="D174" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="175">
@@ -2846,7 +2846,7 @@
         <v>If you're in bad health, a retirement home is a good idea.</v>
       </c>
       <c r="D175" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="176">
@@ -2860,7 +2860,7 @@
         <v>The demand for the commodity would rise, if it were offered for free.</v>
       </c>
       <c r="D176" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="177">
@@ -2874,7 +2874,7 @@
         <v>They were willing to face the harsh conditions and stay in Russia.</v>
       </c>
       <c r="D177" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="178">
@@ -2888,7 +2888,7 @@
         <v xml:space="preserve">We do not have grade budgets. </v>
       </c>
       <c r="D178" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="179">
@@ -2902,7 +2902,7 @@
         <v>The 18th-century Palazzo Grassi would be unpresentable if it was for Gae Aulenti.</v>
       </c>
       <c r="D179" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="180">
@@ -2916,7 +2916,7 @@
         <v>Parents who work with their kids put them at a great disadvantage.</v>
       </c>
       <c r="D180" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="181">
@@ -2930,7 +2930,7 @@
         <v>We didn't learn about this from him.</v>
       </c>
       <c r="D181" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="182">
@@ -2944,7 +2944,7 @@
         <v>Lincoln was not worried and walked slowly.</v>
       </c>
       <c r="D182" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="183">
@@ -2958,7 +2958,7 @@
         <v>I pondered if i made it well.</v>
       </c>
       <c r="D183" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="184">
@@ -2972,7 +2972,7 @@
         <v>I hit you with my little sword.</v>
       </c>
       <c r="D184" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="185">
@@ -2986,7 +2986,7 @@
         <v>It's obvious that we won.</v>
       </c>
       <c r="D185" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="186">
@@ -3000,7 +3000,7 @@
         <v>When there's no sunshine, it feels like I'm living in a cave.</v>
       </c>
       <c r="D186" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="187">
@@ -3014,7 +3014,7 @@
         <v>Walking will get you lost</v>
       </c>
       <c r="D187" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="188">
@@ -3028,7 +3028,7 @@
         <v>The complaints in the ranks did not yield any result.</v>
       </c>
       <c r="D188" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="189">
@@ -3042,7 +3042,7 @@
         <v>Everybody knew that Tommy wasn't nearly smart enough to catch the connection.</v>
       </c>
       <c r="D189" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="190">
@@ -3056,7 +3056,7 @@
         <v>I have reason to suspect that the girl at Manchester was merely a plant.</v>
       </c>
       <c r="D190" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="191">
@@ -3070,7 +3070,7 @@
         <v>Commandments are not a religion.</v>
       </c>
       <c r="D191" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="192">
@@ -3084,7 +3084,7 @@
         <v>If the organization has a clear understanding of its business objectives, it will be able to use the proposed information system to achieve those objectives.</v>
       </c>
       <c r="D192" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="193">
@@ -3098,7 +3098,7 @@
         <v>He would not make a mistake.</v>
       </c>
       <c r="D193" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="194">
@@ -3112,7 +3112,7 @@
         <v>The product is tested for its ability to withstand adverse environmental conditions.</v>
       </c>
       <c r="D194" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="195">
@@ -3126,7 +3126,7 @@
         <v>They will say that they were ready to go.</v>
       </c>
       <c r="D195" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="196">
@@ -3140,7 +3140,7 @@
         <v>We'll have to change the rules.</v>
       </c>
       <c r="D196" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="197">
@@ -3154,7 +3154,7 @@
         <v>I am not at the address.</v>
       </c>
       <c r="D197" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="198">
@@ -3168,7 +3168,7 @@
         <v>The country would be able to control the military.</v>
       </c>
       <c r="D198" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="199">
@@ -3182,7 +3182,7 @@
         <v>If the police believe that the crime was committed by a single person, they will arrest that person.</v>
       </c>
       <c r="D199" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="200">
@@ -3196,7 +3196,7 @@
         <v>I will do it myself.</v>
       </c>
       <c r="D200" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="201">
@@ -3210,7 +3210,7 @@
         <v>The health care system would be under stress if the new policy were implemented.</v>
       </c>
       <c r="D201" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="202">
@@ -3224,7 +3224,7 @@
         <v>I can do it.</v>
       </c>
       <c r="D202" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="203">
@@ -3238,7 +3238,7 @@
         <v>Democrats will win the White House.</v>
       </c>
       <c r="D203" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="204">
@@ -3252,7 +3252,7 @@
         <v>I will write you a letter.</v>
       </c>
       <c r="D204" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="205">
@@ -3266,7 +3266,7 @@
         <v>You can take the train.</v>
       </c>
       <c r="D205" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="206">
@@ -3280,7 +3280,7 @@
         <v>She was sarcastic if she rolled her eyes.</v>
       </c>
       <c r="D206" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="207">
@@ -3294,7 +3294,7 @@
         <v>You are not leaving.</v>
       </c>
       <c r="D207" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="208">
@@ -3308,7 +3308,7 @@
         <v>The cost of testing would be high.</v>
       </c>
       <c r="D208" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="209">
@@ -3322,7 +3322,7 @@
         <v>If you do not get something, you do not deserve it.</v>
       </c>
       <c r="D209" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="210">
@@ -3336,7 +3336,7 @@
         <v>I am not a smart guy.</v>
       </c>
       <c r="D210" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="211">
@@ -3350,7 +3350,7 @@
         <v>The film is the word "misery."</v>
       </c>
       <c r="D211" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="212">
@@ -3364,7 +3364,7 @@
         <v>The man in the moon has no message to send.</v>
       </c>
       <c r="D212" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="213">
@@ -3378,7 +3378,7 @@
         <v>You will end up like me.</v>
       </c>
       <c r="D213" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="214">
@@ -3392,7 +3392,7 @@
         <v>If you can't remember, this conversation is over.</v>
       </c>
       <c r="D214" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="215">
@@ -3406,7 +3406,7 @@
         <v>We will be the only country in the world that does not</v>
       </c>
       <c r="D215" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="216">
@@ -3420,7 +3420,7 @@
         <v>The postal service is not closed.</v>
       </c>
       <c r="D216" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="217">
@@ -3434,7 +3434,7 @@
         <v>The North Vietnamese would not have attacked us if we had not attacked them.</v>
       </c>
       <c r="D217" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="218">
@@ -3448,7 +3448,7 @@
         <v>The idea is not thought through.</v>
       </c>
       <c r="D218" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="219">
@@ -3462,7 +3462,7 @@
         <v>A knife was plunged into my heart.</v>
       </c>
       <c r="D219" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="220">
@@ -3476,7 +3476,7 @@
         <v>If you don't do what I say, you will have to deal with the consequences.</v>
       </c>
       <c r="D220" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="221">
@@ -3490,7 +3490,7 @@
         <v>If you are innocent, you are presumed to be innocent.</v>
       </c>
       <c r="D221" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="222">
@@ -3504,7 +3504,7 @@
         <v>The Senate passed the budget</v>
       </c>
       <c r="D222" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="223">
@@ -3518,7 +3518,7 @@
         <v>You can't be trusted with a gun.</v>
       </c>
       <c r="D223" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="224">
@@ -3532,7 +3532,7 @@
         <v>The standard deviation of the distribution of delivery route profit margins is small.</v>
       </c>
       <c r="D224" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="225">
@@ -3546,7 +3546,7 @@
         <v>The questions are not the same.</v>
       </c>
       <c r="D225" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="226">
@@ -3560,7 +3560,7 @@
         <v>The old adage is true.</v>
       </c>
       <c r="D226" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="227">
@@ -3574,7 +3574,7 @@
         <v>The governor was expected to appoint a special prosecutor.</v>
       </c>
       <c r="D227" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="228">
@@ -3588,7 +3588,7 @@
         <v>The United States would become a banana republic.</v>
       </c>
       <c r="D228" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="229">
@@ -3602,7 +3602,7 @@
         <v>The result is:</v>
       </c>
       <c r="D229" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="230">
@@ -3616,7 +3616,7 @@
         <v>The watchers can only keep a close eye on things if they keep a close eye on the watchers.</v>
       </c>
       <c r="D230" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="231">
@@ -3630,7 +3630,7 @@
         <v>The result of this was to generate more public interest in the arts.</v>
       </c>
       <c r="D231" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="232">
@@ -3644,7 +3644,7 @@
         <v>The root causes of the problem are not being identified.</v>
       </c>
       <c r="D232" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="233">
@@ -3658,7 +3658,7 @@
         <v>The book is magical.</v>
       </c>
       <c r="D233" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="234">
@@ -3672,7 +3672,7 @@
         <v>If you ask for a good table, you will get a good table.</v>
       </c>
       <c r="D234" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="235">
@@ -3686,7 +3686,7 @@
         <v>It is impossible for a similar scenario to occur in the future.</v>
       </c>
       <c r="D235" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="236">
@@ -3700,7 +3700,7 @@
         <v>The fair value of the property transferred is the same as the value of the property received.</v>
       </c>
       <c r="D236" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="237">
@@ -3714,7 +3714,7 @@
         <v>The guy who invented it has a problem with it.</v>
       </c>
       <c r="D237" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="238">
@@ -3728,7 +3728,7 @@
         <v>If we can be said to have a single identity, it is a collective identity.</v>
       </c>
       <c r="D238" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="239">
@@ -3742,7 +3742,7 @@
         <v>Wearing your suit to the party is not unlucky.</v>
       </c>
       <c r="D239" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="240">
@@ -3756,7 +3756,7 @@
         <v>The dog was not in the room, so the noise was not audible.</v>
       </c>
       <c r="D240" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="241">
@@ -3770,7 +3770,7 @@
         <v>The Führer did not order the destruction of the Jews in the concentration camps.</v>
       </c>
       <c r="D241" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="242">
@@ -3784,7 +3784,7 @@
         <v>If you were in my shoes, you would be more careful.</v>
       </c>
       <c r="D242" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="243">
@@ -3798,7 +3798,7 @@
         <v>I know this much is true.</v>
       </c>
       <c r="D243" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="244">
@@ -3812,7 +3812,7 @@
         <v>He was seen as a fool if he had not stopped.</v>
       </c>
       <c r="D244" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="245">
@@ -3826,7 +3826,7 @@
         <v>If I fall asleep, I will miss the movie.</v>
       </c>
       <c r="D245" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="246">
@@ -3840,7 +3840,7 @@
         <v>The facility will not be able to determine whether it is in compliance with the requirements of the rule.</v>
       </c>
       <c r="D246" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="247">
@@ -3854,7 +3854,7 @@
         <v>She looks as if she's just been paid.</v>
       </c>
       <c r="D247" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="248">
@@ -3868,7 +3868,7 @@
         <v>I won't have to.</v>
       </c>
       <c r="D248" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="249">
@@ -3882,7 +3882,7 @@
         <v>The president is a politician.</v>
       </c>
       <c r="D249" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="250">
@@ -3896,7 +3896,7 @@
         <v>If there's no clear threat, it's a good idea to make one up.</v>
       </c>
       <c r="D250" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="251">
@@ -3910,7 +3910,7 @@
         <v>The party will take a stand on the issue.</v>
       </c>
       <c r="D251" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="252">
@@ -3924,7 +3924,7 @@
         <v>The Postal Service will be able to pay its current obligation to the federal government for retiree health benefits at least for the next ten years.</v>
       </c>
       <c r="D252" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="253">
@@ -3938,7 +3938,7 @@
         <v>The crisis will continue to worsen.</v>
       </c>
       <c r="D253" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="254">
@@ -3952,7 +3952,7 @@
         <v>Having a high level of debt is a problem.</v>
       </c>
       <c r="D254" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="255">
@@ -3966,7 +3966,7 @@
         <v>The war is not over.</v>
       </c>
       <c r="D255" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="256">
@@ -3980,7 +3980,7 @@
         <v>The best way to solve the problem is to get rid of all the cars.</v>
       </c>
       <c r="D256" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="257">
@@ -3994,7 +3994,7 @@
         <v>The city council will have to do it.</v>
       </c>
       <c r="D257" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="258">
@@ -4008,7 +4008,7 @@
         <v>If you have a long wait in line, don't go to the snack bar. It is usually full of noisy children.</v>
       </c>
       <c r="D258" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="259">
@@ -4022,7 +4022,7 @@
         <v>If you don't do it, you will regret it.</v>
       </c>
       <c r="D259" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="260">
@@ -4036,7 +4036,7 @@
         <v>The technology of tomorrow is capable of addressing the problems of today.</v>
       </c>
       <c r="D260" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="261">
@@ -4050,7 +4050,7 @@
         <v>The process of socialization and learning that takes place in the family and in the school is interrupted.</v>
       </c>
       <c r="D261" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="262">
@@ -4064,7 +4064,7 @@
         <v>The wine can be made into vinegar.</v>
       </c>
       <c r="D262" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="263">
@@ -4078,7 +4078,7 @@
         <v>The dollar will fall and the yen will rise.</v>
       </c>
       <c r="D263" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="264">
@@ -4092,7 +4092,7 @@
         <v>The amendment will become effective on January 1, 2017.</v>
       </c>
       <c r="D264" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="265">
@@ -4106,7 +4106,7 @@
         <v>The only thing that will save us is if we are able to reach the area of mutual understanding.</v>
       </c>
       <c r="D265" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="266">
@@ -4120,7 +4120,7 @@
         <v>The school district can not issue bonds.</v>
       </c>
       <c r="D266" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="267">
@@ -4134,7 +4134,7 @@
         <v>It is not clear that labor productivity will be adjusted if labor costs are not adjusted.</v>
       </c>
       <c r="D267" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="268">
@@ -4148,7 +4148,7 @@
         <v>The good guys are not necessarily bad.</v>
       </c>
       <c r="D268" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="269">
@@ -4162,7 +4162,7 @@
         <v>Mr. Smithers has seen a ghost.</v>
       </c>
       <c r="D269" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="270">
@@ -4176,7 +4176,7 @@
         <v>The current model is bad.</v>
       </c>
       <c r="D270" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="271">
@@ -4190,7 +4190,7 @@
         <v>Identifying binge drinking in patients isn't strictly determined by the number of drinks had in a single sitting.</v>
       </c>
       <c r="D271" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="272">
@@ -4218,7 +4218,7 @@
         <v>The new contract will go into effect on January 1, 2015.</v>
       </c>
       <c r="D273" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="274">
@@ -4232,7 +4232,7 @@
         <v>I would have known how to do it.</v>
       </c>
       <c r="D274" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="275">
@@ -4246,7 +4246,7 @@
         <v>If you are not too much of a perfectionist, you will be able to make a good product.</v>
       </c>
       <c r="D275" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="276">
@@ -4260,7 +4260,7 @@
         <v>The financial sector is not important.</v>
       </c>
       <c r="D276" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="277">
@@ -4274,7 +4274,7 @@
         <v>The appropriate next step is to contact the Intake program for a referral to the Intake II program.</v>
       </c>
       <c r="D277" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="278">
@@ -4288,7 +4288,7 @@
         <v>The soldiers are already dead.</v>
       </c>
       <c r="D278" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="279">
@@ -4302,7 +4302,7 @@
         <v>I have to find a job.</v>
       </c>
       <c r="D279" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="280">
@@ -4316,7 +4316,7 @@
         <v>He said he would go with me to a concert at the Albert Hall.</v>
       </c>
       <c r="D280" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="281">
@@ -4330,7 +4330,7 @@
         <v>I have not yet read it.</v>
       </c>
       <c r="D281" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="282">
@@ -4344,7 +4344,7 @@
         <v>If the current interest rate stays the same, the treasury security market price stays the same.</v>
       </c>
       <c r="D282" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="283">
@@ -4358,7 +4358,7 @@
         <v>Non-profits do not have the power to change the world.</v>
       </c>
       <c r="D283" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="284">
@@ -4372,7 +4372,7 @@
         <v>I would have done so, if I were in a position to help.</v>
       </c>
       <c r="D284" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="285">
@@ -4386,7 +4386,7 @@
         <v>The machine was not the worker's boss.</v>
       </c>
       <c r="D285" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="286">
@@ -4400,7 +4400,7 @@
         <v>You're sure.</v>
       </c>
       <c r="D286" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="287">
@@ -4414,7 +4414,7 @@
         <v>This will have to be re-evaluated.</v>
       </c>
       <c r="D287" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="288">
@@ -4428,7 +4428,7 @@
         <v>I think you are very clever.</v>
       </c>
       <c r="D288" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="289">
@@ -4442,7 +4442,7 @@
         <v>He would have answered anyway.</v>
       </c>
       <c r="D289" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="290">
@@ -4456,7 +4456,7 @@
         <v>They can't afford to go to the movies.</v>
       </c>
       <c r="D290" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="291">
@@ -4470,7 +4470,7 @@
         <v>If you have to have an argument, have it with your girlfriend.</v>
       </c>
       <c r="D291" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="292">
@@ -4484,7 +4484,7 @@
         <v>If we have a pair of opposites, we can always get a false dichotomy.</v>
       </c>
       <c r="D292" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="293">
@@ -4498,7 +4498,7 @@
         <v>The company will be put out of business.</v>
       </c>
       <c r="D293" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="294">
@@ -4512,7 +4512,7 @@
         <v>The country has no interest in the problem, because the media has decided to ignore it.</v>
       </c>
       <c r="D294" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="295">
@@ -4526,7 +4526,7 @@
         <v>The child is not illegitimate.</v>
       </c>
       <c r="D295" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="296">
@@ -4540,7 +4540,7 @@
         <v>If the new legislation is passed, a separate Ministry of Women's Affairs will be created.</v>
       </c>
       <c r="D296" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="297">
@@ -4554,7 +4554,7 @@
         <v>The military has been greatly reduced in size.</v>
       </c>
       <c r="D297" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="298">
@@ -4568,7 +4568,7 @@
         <v>If you don't do the repairs, you will be responsible for the entire cost of the repairs.</v>
       </c>
       <c r="D298" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="299">
@@ -4582,7 +4582,7 @@
         <v>If you have a complaint, write to the president.</v>
       </c>
       <c r="D299" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="300">
@@ -4596,7 +4596,7 @@
         <v>I knew that you would tell me.</v>
       </c>
       <c r="D300" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="301">
@@ -4610,7 +4610,7 @@
         <v>The chef's special of the day is a good place to have dinner.</v>
       </c>
       <c r="D301" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="302">
@@ -4624,7 +4624,7 @@
         <v>Brook tried Thai food for the first time</v>
       </c>
       <c r="D302" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="303">
@@ -4638,7 +4638,7 @@
         <v>P60 is the letter from a school board member to the editor in which they retell what happens in the case.</v>
       </c>
       <c r="D303" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="304">
@@ -4652,7 +4652,7 @@
         <v>School libraries have yearbooks.</v>
       </c>
       <c r="D304" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="305">
@@ -4666,7 +4666,7 @@
         <v>This story was reported by a man</v>
       </c>
       <c r="D305" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="306">
@@ -4680,7 +4680,7 @@
         <v>The guide does not advise people to prepare the coffee in the middle of the day.</v>
       </c>
       <c r="D306" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="307">
@@ -4694,7 +4694,7 @@
         <v>I did not get along well with jason</v>
       </c>
       <c r="D307" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="308">
@@ -4708,7 +4708,7 @@
         <v>They were referring to a violin.</v>
       </c>
       <c r="D308" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="309">
@@ -4722,7 +4722,7 @@
         <v>Some substances need to be taken off the market due to their environmental impact.</v>
       </c>
       <c r="D309" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="310">
@@ -4736,7 +4736,7 @@
         <v>The commission is considering a proposal on wind power.</v>
       </c>
       <c r="D310" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="311">
@@ -4750,7 +4750,7 @@
         <v>The man despises Germany.</v>
       </c>
       <c r="D311" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="312">
@@ -4764,7 +4764,7 @@
         <v>Water will be needed</v>
       </c>
       <c r="D312" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="313">
@@ -4778,7 +4778,7 @@
         <v>Mark Cavendish pulled out of the Tour de France.</v>
       </c>
       <c r="D313" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="314">
@@ -4792,7 +4792,7 @@
         <v>After you indicate why you think she is a good source for your story, wait until after the interview to blackmail them.</v>
       </c>
       <c r="D314" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="315">
@@ -4806,7 +4806,7 @@
         <v>The royalists only wear yellow</v>
       </c>
       <c r="D315" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="316">
@@ -4820,7 +4820,7 @@
         <v>think about a good memory can be usefull to write a letter</v>
       </c>
       <c r="D316" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="317">
@@ -4834,7 +4834,7 @@
         <v>the right arrow showed the correct way</v>
       </c>
       <c r="D317" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="318">
@@ -4848,7 +4848,7 @@
         <v>Some fruits are best avoided</v>
       </c>
       <c r="D318" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="319">
@@ -4862,7 +4862,7 @@
         <v>Tie Dye will be eighteen on his next birthday.</v>
       </c>
       <c r="D319" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="320">
@@ -4876,7 +4876,7 @@
         <v>The new student needed to be shown around.</v>
       </c>
       <c r="D320" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="321">
@@ -4890,7 +4890,7 @@
         <v>Europeans are peacekeepers in Bosnia</v>
       </c>
       <c r="D321" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="322">
@@ -4904,7 +4904,7 @@
         <v>The horse needs to be a tame horse.</v>
       </c>
       <c r="D322" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="323">
@@ -4918,7 +4918,7 @@
         <v>The process can be used to rip DVDs.</v>
       </c>
       <c r="D323" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="324">
@@ -4932,7 +4932,7 @@
         <v>The inspector certified it but was aware of the issues</v>
       </c>
       <c r="D324" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="325">
@@ -4946,7 +4946,7 @@
         <v>Suzy needed a trim</v>
       </c>
       <c r="D325" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="326">
@@ -4960,7 +4960,7 @@
         <v>It was a used toy</v>
       </c>
       <c r="D326" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="327">
@@ -4974,7 +4974,7 @@
         <v>Guns are expensive and the police need the money redirected to them.</v>
       </c>
       <c r="D327" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="328">
@@ -4988,7 +4988,7 @@
         <v>Maya hated her school.</v>
       </c>
       <c r="D328" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="329">
@@ -5002,7 +5002,7 @@
         <v xml:space="preserve">The last statement in this context is a sarcastic remark. </v>
       </c>
       <c r="D329" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="330">
@@ -5016,7 +5016,7 @@
         <v xml:space="preserve"> Randy only drinks 11% of drinks he buy</v>
       </c>
       <c r="D330" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="331">
@@ -5030,7 +5030,7 @@
         <v>Be sure to wash your hands first using an antibacterial soap, and to rinse them well with a lot of dirt.</v>
       </c>
       <c r="D331" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="332">
@@ -5044,7 +5044,7 @@
         <v>Hellgate was released in American before Thailand</v>
       </c>
       <c r="D332" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="333">
@@ -5058,7 +5058,7 @@
         <v>His office has acted as supervisor of the various privacy codes for many years.</v>
       </c>
       <c r="D333" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="334">
@@ -5072,7 +5072,7 @@
         <v>Sarah did not buy cabbage juice.</v>
       </c>
       <c r="D334" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="335">
@@ -5086,7 +5086,7 @@
         <v>Dire Straits never wanted to be popular in the United States.</v>
       </c>
       <c r="D335" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="336">
@@ -5100,7 +5100,7 @@
         <v>Healthy folks never get sick.</v>
       </c>
       <c r="D336" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="337">
@@ -5114,7 +5114,7 @@
         <v>Ethan visted Americas neighbor</v>
       </c>
       <c r="D337" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="338">
@@ -5128,7 +5128,7 @@
         <v>The budgetary measures include loans that are paid off.</v>
       </c>
       <c r="D338" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="339">
@@ -5142,7 +5142,7 @@
         <v>Tim needs new trays</v>
       </c>
       <c r="D339" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="340">
@@ -5156,7 +5156,7 @@
         <v>Tim ended up dumping his fiancee before the wedding because of the bachelor party.</v>
       </c>
       <c r="D340" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="341">
@@ -5170,7 +5170,7 @@
         <v>Gun laws are crucial but not loving children</v>
       </c>
       <c r="D341" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="342">
@@ -5184,7 +5184,7 @@
         <v>The Privacy Commissioner has been an advocate for supervision</v>
       </c>
       <c r="D342" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="343">
@@ -5198,7 +5198,7 @@
         <v>Steven has swam for a long time</v>
       </c>
       <c r="D343" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="344">
@@ -5212,7 +5212,7 @@
         <v>The Tasmanian Legislative Council wants to move out of Hobart.</v>
       </c>
       <c r="D344" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="345">
@@ -5226,7 +5226,7 @@
         <v>They support the north alliance treaty</v>
       </c>
       <c r="D345" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="346">
@@ -5240,7 +5240,7 @@
         <v xml:space="preserve">Feeding newborn puppies requires lots of supplies. </v>
       </c>
       <c r="D346" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="347">
@@ -5254,7 +5254,7 @@
         <v xml:space="preserve">Parasailing was a dream come true for Lucy. </v>
       </c>
       <c r="D347" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="348">
@@ -5268,7 +5268,7 @@
         <v>Uncle Sam called his first album "Uncle Sammy"</v>
       </c>
       <c r="D348" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="349">
@@ -5282,7 +5282,7 @@
         <v xml:space="preserve">The plaintiff objects to the judge's comments being on record.  </v>
       </c>
       <c r="D349" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="350">
@@ -5296,7 +5296,7 @@
         <v>Reba lost her watch to a mugger.</v>
       </c>
       <c r="D350" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="351">
@@ -5310,7 +5310,7 @@
         <v>Put a frying pan on the stove.</v>
       </c>
       <c r="D351" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="352">
@@ -5324,7 +5324,7 @@
         <v>He has directed such films as "Hank and the Search for Happiness", "Serendipity", and "Shall We Dance?"</v>
       </c>
       <c r="D352" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="353">
@@ -5338,7 +5338,7 @@
         <v xml:space="preserve">The solution is not based on an active fight against the Colombian drug mafia. </v>
       </c>
       <c r="D353" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="354">
@@ -5352,7 +5352,7 @@
         <v>A very big chair is needed to make a watermelon smoothie using a drill</v>
       </c>
       <c r="D354" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="355">
@@ -5366,7 +5366,7 @@
         <v>Josh misses his home</v>
       </c>
       <c r="D355" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="356">
@@ -5380,7 +5380,7 @@
         <v>The president started a war.</v>
       </c>
       <c r="D356" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="357">
@@ -5394,7 +5394,7 @@
         <v>my husband was correct about me being bad at golf</v>
       </c>
       <c r="D357" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="358">
@@ -5408,7 +5408,7 @@
         <v>Alejandro Ghersi is a mexican producer</v>
       </c>
       <c r="D358" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="359">
@@ -5422,7 +5422,7 @@
         <v>they left at nine thirty AM.</v>
       </c>
       <c r="D359" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="360">
@@ -5436,7 +5436,7 @@
         <v>The Conservative Party in Canada wants to discuss affordable housing in the house of commons.</v>
       </c>
       <c r="D360" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="361">
@@ -5450,7 +5450,7 @@
         <v>cyanide is not needed</v>
       </c>
       <c r="D361" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="362">
@@ -5464,7 +5464,7 @@
         <v>She flew over the river.</v>
       </c>
       <c r="D362" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="363">
@@ -5478,7 +5478,7 @@
         <v>The narrator wants to know if Mr. Landry was given all the information</v>
       </c>
       <c r="D363" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="364">
@@ -5492,7 +5492,7 @@
         <v>I hope the Minister of Human Species Development and her officials will really take note of what I said</v>
       </c>
       <c r="D364" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="365">
@@ -5506,7 +5506,7 @@
         <v>Running the 100 meter sprint requires little endurance training</v>
       </c>
       <c r="D365" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="366">
@@ -5520,7 +5520,7 @@
         <v>Alan Metter has directed war films.</v>
       </c>
       <c r="D366" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="367">
@@ -5534,7 +5534,7 @@
         <v>The Islamic Jihad wants it's leader released and the embargo on Iran lifted.</v>
       </c>
       <c r="D367" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="368">
@@ -5548,7 +5548,7 @@
         <v>anna interacts with people</v>
       </c>
       <c r="D368" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="369">
@@ -5562,7 +5562,7 @@
         <v>The tree fell over.</v>
       </c>
       <c r="D369" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="370">
@@ -5576,7 +5576,7 @@
         <v>Labour legislation has advanced in the House.</v>
       </c>
       <c r="D370" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="371">
@@ -5590,7 +5590,7 @@
         <v>Kevin Vincent, 44, of Arlington, Va., said his wife buys aleve brand acetaminophen and he wanted to find out more about the problem</v>
       </c>
       <c r="D371" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="372">
@@ -5604,7 +5604,7 @@
         <v>The red shirts are supports of the rural and poor and support the Prime Minister.</v>
       </c>
       <c r="D372" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="373">
@@ -5618,7 +5618,7 @@
         <v>Randy bought some vodka.</v>
       </c>
       <c r="D373" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="374">
@@ -5632,7 +5632,7 @@
         <v>The citizens did not want a new president</v>
       </c>
       <c r="D374" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="375">
@@ -5646,7 +5646,7 @@
         <v>Braun Strowman has a problem with Brock Lesnar.</v>
       </c>
       <c r="D375" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="376">
@@ -5660,7 +5660,7 @@
         <v>Ethan ate italian food</v>
       </c>
       <c r="D376" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="377">
@@ -5674,7 +5674,7 @@
         <v xml:space="preserve">Your data plan is decided by your phone carrier. </v>
       </c>
       <c r="D377" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="378">
@@ -5688,7 +5688,7 @@
         <v>The Governor told Caleb to keep on the near side of the road going home.</v>
       </c>
       <c r="D378" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="379">
@@ -5702,7 +5702,7 @@
         <v>Rufus Wainwright's "I Don't Know What It Is" was released after his second album but before July 27, 2004.</v>
       </c>
       <c r="D379" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="380">
@@ -5716,7 +5716,7 @@
         <v>In the 1950s, the United States FBI began to maintain a public list of the people it regarded as the Ten Most Wanted Villians</v>
       </c>
       <c r="D380" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="381">
@@ -5730,7 +5730,7 @@
         <v>The second step to becoming a good boss in a particular role is having an excellent understanding of the job and what is needed to be successful</v>
       </c>
       <c r="D381" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="382">
@@ -5744,7 +5744,7 @@
         <v>An anonymous text does not reveal your name.</v>
       </c>
       <c r="D382" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="383">
@@ -5758,7 +5758,7 @@
         <v>Bath, Maine and Sagadahoc County were respresented by the Democratic Floor Leader, Mary Small.</v>
       </c>
       <c r="D383" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="384">
@@ -5772,7 +5772,7 @@
         <v>kates daughter is antisocial</v>
       </c>
       <c r="D384" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="385">
@@ -5786,7 +5786,7 @@
         <v>Pamunuwa isn't located within the Easter Province.</v>
       </c>
       <c r="D385" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="386">
@@ -5800,7 +5800,7 @@
         <v>Puppies contains three instances of the letter p.</v>
       </c>
       <c r="D386" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="387">
@@ -5814,7 +5814,7 @@
         <v>Sammy practiced baseball with diligence.</v>
       </c>
       <c r="D387" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="388">
@@ -5828,7 +5828,7 @@
         <v>Steven's childhood hobby became a career</v>
       </c>
       <c r="D388" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="389">
@@ -5842,7 +5842,7 @@
         <v xml:space="preserve">The people in thegovernment are blaming each other and being hateful. </v>
       </c>
       <c r="D389" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="390">
@@ -5856,7 +5856,7 @@
         <v>What a Girl Wants earned a silver certification in Belgium.</v>
       </c>
       <c r="D390" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="391">
@@ -5870,7 +5870,7 @@
         <v>Anorexia nervosa is wrongly believed to be characterized by food restriction.</v>
       </c>
       <c r="D391" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="392">
@@ -5884,7 +5884,7 @@
         <v>Tina Turner made a song for an Indiana Jones film.</v>
       </c>
       <c r="D392" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="393">
@@ -5898,7 +5898,7 @@
         <v>Wyatt Earp was a human.</v>
       </c>
       <c r="D393" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="394">
@@ -5912,7 +5912,7 @@
         <v>Tina Turner made a song for Golden Eye.</v>
       </c>
       <c r="D394" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="395">
@@ -5926,7 +5926,7 @@
         <v>Demi Lovato is an advocate for snacks.</v>
       </c>
       <c r="D395" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="396">
@@ -5940,7 +5940,7 @@
         <v>DJ Khaled changed his name after September 11, 2008.</v>
       </c>
       <c r="D396" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="397">
@@ -5954,7 +5954,7 @@
         <v>Barbara Bush founded the Barbara Bush Foundation for Child Literacy.</v>
       </c>
       <c r="D397" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="398">
@@ -5968,7 +5968,7 @@
         <v>Randall Flagg has been featured in The Stand and Dark Tower.</v>
       </c>
       <c r="D398" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="399">
@@ -5982,7 +5982,7 @@
         <v>What a Girl Wants earned a gold certification in the U.S.</v>
       </c>
       <c r="D399" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="400">
@@ -5996,7 +5996,7 @@
         <v>Megan Fox worked with Faith Ford.</v>
       </c>
       <c r="D400" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="401">
@@ -6010,7 +6010,7 @@
         <v>The Dark Knight takes place in Gotham City.</v>
       </c>
       <c r="D401" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="402">
@@ -6024,7 +6024,7 @@
         <v>Fight Club stars Brad Pitt.</v>
       </c>
       <c r="D402" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="403">
@@ -6038,7 +6038,7 @@
         <v>Everybody Needs a Best Friend is from a YouTube video.</v>
       </c>
       <c r="D403" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="404">
@@ -6052,7 +6052,7 @@
         <v>Doctor Who travels alone</v>
       </c>
       <c r="D404" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="405">
@@ -6066,7 +6066,7 @@
         <v>Helen Hunt was in 5 films where Helen Hunt ate a burger.</v>
       </c>
       <c r="D405" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="406">
@@ -6080,7 +6080,7 @@
         <v>Jeff Bezos is the founder of Facebook.</v>
       </c>
       <c r="D406" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="407">
@@ -6094,7 +6094,7 @@
         <v>Tina Turner's album Break Every Rule went gold.</v>
       </c>
       <c r="D407" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="408">
@@ -6108,7 +6108,7 @@
         <v>Doc Holliday never set up practice in Atlanta.</v>
       </c>
       <c r="D408" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="409">
@@ -6122,7 +6122,7 @@
         <v>Psychology is discipline within academia.</v>
       </c>
       <c r="D409" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="410">
@@ -6136,7 +6136,7 @@
         <v>Narendra Modi is an Indian politician.</v>
       </c>
       <c r="D410" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="411">
@@ -6150,7 +6150,7 @@
         <v>Doctor Who has been played by multiple performers</v>
       </c>
       <c r="D411" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="412">
@@ -6164,7 +6164,7 @@
         <v>Kaplan wants to see his vision through.</v>
       </c>
       <c r="D412" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="413">
@@ -6178,7 +6178,7 @@
         <v>He was given a report with what he wanted being shown annually.</v>
       </c>
       <c r="D413" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="414">
@@ -6192,7 +6192,7 @@
         <v>These Kosher laws have allowed protected animals to thrive.</v>
       </c>
       <c r="D414" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="415">
@@ -6206,7 +6206,7 @@
         <v>Abbe Lowell plans to attempt capitalization on Starr's questioning.</v>
       </c>
       <c r="D415" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="416">
@@ -6220,7 +6220,7 @@
         <v>The press needs to be restructured to get rid of any leaking</v>
       </c>
       <c r="D416" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="417">
@@ -6234,7 +6234,7 @@
         <v>Klayman wants others to believe he's coherent.</v>
       </c>
       <c r="D417" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="418">
@@ -6248,7 +6248,7 @@
         <v>The world will run with good guidance with macroeconomics.</v>
       </c>
       <c r="D418" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="419">
@@ -6262,7 +6262,7 @@
         <v>Joyce can't find the piece she's looking for.</v>
       </c>
       <c r="D419" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="420">
@@ -6276,7 +6276,7 @@
         <v>The author made the question vague on purpose.</v>
       </c>
       <c r="D420" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="421">
@@ -6290,7 +6290,7 @@
         <v>The woman does not have a dying wish.</v>
       </c>
       <c r="D421" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="422">
@@ -6304,7 +6304,7 @@
         <v>Despite some high hopes in its promising start, the brand has been on a steady decline.</v>
       </c>
       <c r="D422" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="423">
@@ -6318,7 +6318,7 @@
         <v>All basset hounds have good sense.</v>
       </c>
       <c r="D423" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="424">
@@ -6332,7 +6332,7 @@
         <v>I like all Mazda cars.</v>
       </c>
       <c r="D424" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="425">
@@ -6346,7 +6346,7 @@
         <v>They need to be listened to.</v>
       </c>
       <c r="D425" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="426">
@@ -6360,7 +6360,7 @@
         <v>They needed to know the name of the man.</v>
       </c>
       <c r="D426" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="427">
@@ -6374,7 +6374,7 @@
         <v>Greenspan's statement needed restatement.</v>
       </c>
       <c r="D427" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="428">
@@ -6402,7 +6402,7 @@
         <v>The woman is single.</v>
       </c>
       <c r="D429" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="430">
@@ -6416,7 +6416,7 @@
         <v>Katz desperately wants to be published by the Washington Post.</v>
       </c>
       <c r="D430" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="431">
@@ -6430,7 +6430,7 @@
         <v>Microsoft is a powerful player in their market, with the ability to neutralize problems.</v>
       </c>
       <c r="D431" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="432">
@@ -6444,7 +6444,7 @@
         <v>Springer is not popular.</v>
       </c>
       <c r="D432" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="433">
@@ -6458,7 +6458,7 @@
         <v>Everyone ought to mind their own business regarding her love life.</v>
       </c>
       <c r="D433" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="434">
@@ -6472,7 +6472,7 @@
         <v>Inglis built a long trait of highway</v>
       </c>
       <c r="D434" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="435">
@@ -6486,7 +6486,7 @@
         <v>There are still those that want to give gifts.</v>
       </c>
       <c r="D435" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="436">
@@ -6500,7 +6500,7 @@
         <v>The soldiers wanted to help her</v>
       </c>
       <c r="D436" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="437">
@@ -6514,7 +6514,7 @@
         <v>McCain wants to increase taxes for everyone.</v>
       </c>
       <c r="D437" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="438">
@@ -6528,7 +6528,7 @@
         <v>The protagonist and her brothers grow up in Japan.</v>
       </c>
       <c r="D438" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="439">
@@ -6542,7 +6542,7 @@
         <v>The parolee has always followed the law</v>
       </c>
       <c r="D439" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="440">
@@ -6556,7 +6556,7 @@
         <v>Jesse Ventura does not want Pat to win the nomination.</v>
       </c>
       <c r="D440" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="441">
@@ -6570,7 +6570,7 @@
         <v>The new technology throws breaking stories into a newspaper.</v>
       </c>
       <c r="D441" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="442">
@@ -6584,7 +6584,7 @@
         <v>It is a small amount, compared to what's needed.</v>
       </c>
       <c r="D442" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="443">
@@ -6598,7 +6598,7 @@
         <v>The kirkbuzzers'* guild needs money from him</v>
       </c>
       <c r="D443" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="444">
@@ -6612,7 +6612,7 @@
         <v>Republicans often seek to give back to their poor constituents when there is a budget deficit.</v>
       </c>
       <c r="D444" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="445">
@@ -6626,7 +6626,7 @@
         <v>PointCast is trying to make it's first software product as a firm.</v>
       </c>
       <c r="D445" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="446">
@@ -6640,7 +6640,7 @@
         <v>Bettelheim focused on the importance of being a guide</v>
       </c>
       <c r="D446" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="447">
@@ -6654,7 +6654,7 @@
         <v>Critics who are frantic about saving the novel today wanted to kill it 40 years ago.</v>
       </c>
       <c r="D447" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="448">
@@ -6668,7 +6668,7 @@
         <v>Pollock's career was short</v>
       </c>
       <c r="D448" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="449">
@@ -6682,7 +6682,7 @@
         <v>Woman serves the man's need for speed</v>
       </c>
       <c r="D449" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="450">
@@ -6696,7 +6696,7 @@
         <v>Cutting social payment systems generates heat for national leaders.</v>
       </c>
       <c r="D450" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="451">
@@ -6710,7 +6710,7 @@
         <v>European governments put large taxes on call-back services.</v>
       </c>
       <c r="D451" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="452">
@@ -6724,7 +6724,7 @@
         <v>The federal government knows that disaster money is well sought after.</v>
       </c>
       <c r="D452" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="453">
@@ -6738,7 +6738,7 @@
         <v>I am completely happy with how it is going</v>
       </c>
       <c r="D453" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="454">
@@ -6752,7 +6752,7 @@
         <v>Some want to give up on special prosecutors.</v>
       </c>
       <c r="D454" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="455">
@@ -6766,7 +6766,7 @@
         <v xml:space="preserve">I want to find Gabriel's Fire; it is my favourite. </v>
       </c>
       <c r="D455" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="456">
@@ -6780,7 +6780,7 @@
         <v>The LSC had doubts about the effectiveness of the guidance proposed.</v>
       </c>
       <c r="D456" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="457">
@@ -6794,7 +6794,7 @@
         <v xml:space="preserve">Tommy really wanted to know. </v>
       </c>
       <c r="D457" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="458">
@@ -6808,7 +6808,7 @@
         <v>This review will attempt to disprove the reason for intervening.</v>
       </c>
       <c r="D458" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="459">
@@ -6822,7 +6822,7 @@
         <v>It is impossible to know if the legislation is effective.</v>
       </c>
       <c r="D459" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="460">
@@ -6836,7 +6836,7 @@
         <v>Looking at what the cans contained made him want to vomit.</v>
       </c>
       <c r="D460" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="461">
@@ -6850,7 +6850,7 @@
         <v xml:space="preserve">She was nervous even though she didn't want to be. </v>
       </c>
       <c r="D461" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="462">
@@ -6864,7 +6864,7 @@
         <v xml:space="preserve">My son really wants to have a dog.  </v>
       </c>
       <c r="D462" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="463">
@@ -6878,7 +6878,7 @@
         <v>Demands on training and supervision are increased with multiple sites.</v>
       </c>
       <c r="D463" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="464">
@@ -6892,7 +6892,7 @@
         <v>While he liked his environment generally, he wanted to leave shortly to avoid the autumn torrents.</v>
       </c>
       <c r="D464" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="465">
@@ -6906,7 +6906,7 @@
         <v>Spock tried to cheat on his wife.</v>
       </c>
       <c r="D465" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="466">
@@ -6920,7 +6920,7 @@
         <v xml:space="preserve">The price needed to be capped. </v>
       </c>
       <c r="D466" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="467">
@@ -6934,7 +6934,7 @@
         <v>My husband is happy to let me take care of the flowers, while he maintains the lawn just the way he likes it.</v>
       </c>
       <c r="D467" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="468">
@@ -6948,7 +6948,7 @@
         <v>They've really made a mess of our family reunion.</v>
       </c>
       <c r="D468" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="469">
@@ -6962,7 +6962,7 @@
         <v xml:space="preserve">I wanted to buy a house with a deck, but I decided to get one without. </v>
       </c>
       <c r="D469" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="470">
@@ -6976,7 +6976,7 @@
         <v>The Party wants him to leave ASAP.</v>
       </c>
       <c r="D470" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="471">
@@ -6990,7 +6990,7 @@
         <v>I decided I didn't need to eat.</v>
       </c>
       <c r="D471" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="472">
@@ -7004,7 +7004,7 @@
         <v xml:space="preserve">Vrenna wants to know if the Kal is going. </v>
       </c>
       <c r="D472" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="473">
@@ -7018,7 +7018,7 @@
         <v>There were no agents who were willing to lie for Clinton in any case.</v>
       </c>
       <c r="D473" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="474">
@@ -7032,7 +7032,7 @@
         <v>We wanted to wire Lewinsky.</v>
       </c>
       <c r="D474" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="475">
@@ -7046,7 +7046,7 @@
         <v>Functional and advocate needs are always in sync.</v>
       </c>
       <c r="D475" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="476">
@@ -7060,7 +7060,7 @@
         <v xml:space="preserve">Drew didn't want to run Shannon down. </v>
       </c>
       <c r="D476" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="477">
@@ -7074,7 +7074,7 @@
         <v>They really make the family reunion process easy.</v>
       </c>
       <c r="D477" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="478">
@@ -7088,7 +7088,7 @@
         <v>I hope I see it someday.</v>
       </c>
       <c r="D478" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="479">
@@ -7102,7 +7102,7 @@
         <v>During this time, the Bushes didn't want anything to do with me.</v>
       </c>
       <c r="D479" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="480">
@@ -7116,7 +7116,7 @@
         <v>We need to remember some ideas..</v>
       </c>
       <c r="D480" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="481">
@@ -7130,7 +7130,7 @@
         <v>The astronomer was baffled by the question of why people would want coal and oil even though they have been to space and asked for reasons for the confusion.</v>
       </c>
       <c r="D481" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="482">
@@ -7144,7 +7144,7 @@
         <v>The GAO and IGs need to have solid relationships.</v>
       </c>
       <c r="D482" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="483">
@@ -7158,7 +7158,7 @@
         <v>Thank you for your persistence in reminding me whenever I have tried to be emotional.</v>
       </c>
       <c r="D483" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="484">
@@ -7172,7 +7172,7 @@
         <v>We want kids.</v>
       </c>
       <c r="D484" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="485">
@@ -7186,7 +7186,7 @@
         <v>We had the desire to create a bit of hope through the HRC logo.</v>
       </c>
       <c r="D485" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="486">
@@ -7200,7 +7200,7 @@
         <v>I completely paved my driveway the following spring.</v>
       </c>
       <c r="D486" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="487">
@@ -7214,7 +7214,7 @@
         <v xml:space="preserve">Jackson needs help </v>
       </c>
       <c r="D487" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="488">
@@ -7228,7 +7228,7 @@
         <v>The second stage was planned at the end of the 17th century.</v>
       </c>
       <c r="D488" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="489">
@@ -7242,7 +7242,7 @@
         <v xml:space="preserve">I needed to leave. </v>
       </c>
       <c r="D489" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="490">
@@ -7270,7 +7270,7 @@
         <v>Gilder doesn't need any excuse to write technical writing.</v>
       </c>
       <c r="D491" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="492">
@@ -7284,7 +7284,7 @@
         <v>Good leaders can help an organization overcome its resistance to change.</v>
       </c>
       <c r="D492" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="493">
@@ -7298,7 +7298,7 @@
         <v>It needs to be wound constantly and is accurate to within five minutes.</v>
       </c>
       <c r="D493" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="494">
@@ -7312,7 +7312,7 @@
         <v>They knew the power of being informed.</v>
       </c>
       <c r="D494" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="495">
@@ -7326,7 +7326,7 @@
         <v>It was difficult to find where his office is.</v>
       </c>
       <c r="D495" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="496">
@@ -7340,7 +7340,7 @@
         <v>I think I want to be him.</v>
       </c>
       <c r="D496" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="497">
@@ -7354,7 +7354,7 @@
         <v>He needs the time.</v>
       </c>
       <c r="D497" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="498">
@@ -7368,7 +7368,7 @@
         <v>The residents wanted to get their mail at 8:00 a.m.</v>
       </c>
       <c r="D498" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="499">
@@ -7382,7 +7382,7 @@
         <v>Because they were Hindu, Nehru's Congress Party was lead by socialists.</v>
       </c>
       <c r="D499" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="500">
@@ -7396,7 +7396,7 @@
         <v>Cynthia was allergic to the grass, and wouldn't touch it.</v>
       </c>
       <c r="D500" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="501">
@@ -7410,7 +7410,7 @@
         <v>Bombing countries tanks your approval rating.</v>
       </c>
       <c r="D501" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="502">
@@ -7424,7 +7424,7 @@
         <v>Fridlund-Hume warned against trying too hard to seem right.</v>
       </c>
       <c r="D502" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="503">
@@ -7438,7 +7438,7 @@
         <v>In the Soviet Union, there are a lot of different cultures trying to make it work in one country.</v>
       </c>
       <c r="D503" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="504">
@@ -7452,7 +7452,7 @@
         <v>I'm not able to wear whatever I want while working from home unfortunately.</v>
       </c>
       <c r="D504" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="505">
@@ -7466,7 +7466,7 @@
         <v>I want you to be free to make the choices you desire.</v>
       </c>
       <c r="D505" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="506">
@@ -7480,7 +7480,7 @@
         <v>You do need to keep track of the major cobbled streets, though.</v>
       </c>
       <c r="D506" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="507">
@@ -7494,7 +7494,7 @@
         <v>I know Panama takes drugs very seriously.</v>
       </c>
       <c r="D507" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="508">
@@ -7508,7 +7508,7 @@
         <v>The included quiz can be used to diagnose medical issues.</v>
       </c>
       <c r="D508" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="509">
@@ -7522,7 +7522,7 @@
         <v>want to be involved in the excitement</v>
       </c>
       <c r="D509" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="510">
@@ -7536,7 +7536,7 @@
         <v>The chairman wants to maintain the strength of the mission.</v>
       </c>
       <c r="D510" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="511">
@@ -7550,7 +7550,7 @@
         <v>Berman sails across the ocean on a spiritual voyage.</v>
       </c>
       <c r="D511" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="512">
@@ -7564,7 +7564,7 @@
         <v>I want to tell her not to say that.</v>
       </c>
       <c r="D512" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="513">
@@ -7578,7 +7578,7 @@
         <v>I'm going to force Emily into being the way I want her</v>
       </c>
       <c r="D513" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="514">
@@ -7592,7 +7592,7 @@
         <v>Pro-choicers in the 70s did not want to associate with the emerging feminist movement.</v>
       </c>
       <c r="D514" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="515">
@@ -7606,7 +7606,7 @@
         <v>It is clear that he does not need to use a method to be successful.</v>
       </c>
       <c r="D515" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="516">
@@ -7620,7 +7620,7 @@
         <v>You need binoculars to get a good look at the third tier of arches.</v>
       </c>
       <c r="D516" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="517">
@@ -7634,7 +7634,7 @@
         <v>You just wish he committed that crime?</v>
       </c>
       <c r="D517" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="518">
@@ -7648,7 +7648,7 @@
         <v>"I do not wish to sell food to those incapable of appreciate its true, pleasing nature," he replied.</v>
       </c>
       <c r="D518" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="519">
@@ -7662,7 +7662,7 @@
         <v>Tokyo's reconstruction was poorly planned.</v>
       </c>
       <c r="D519" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="520">
@@ -7676,7 +7676,7 @@
         <v>They wanted me to plant the roses by their entryway.</v>
       </c>
       <c r="D520" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="521">
@@ -7690,7 +7690,7 @@
         <v>The first website function redirects you to the home page.</v>
       </c>
       <c r="D521" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="522">
@@ -7704,7 +7704,7 @@
         <v>Ryerson thinks that tougher laws are needed for environmental protection</v>
       </c>
       <c r="D522" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="523">
@@ -7718,7 +7718,7 @@
         <v>He wanted teens in poverty to use measures to prevent them from barring children.</v>
       </c>
       <c r="D523" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="524">
@@ -7732,7 +7732,7 @@
         <v>I'm in the middle of bids because I want my house painted.</v>
       </c>
       <c r="D524" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="525">
@@ -7746,7 +7746,7 @@
         <v>They needed an extra income</v>
       </c>
       <c r="D525" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="526">
@@ -7760,7 +7760,7 @@
         <v>I do what I want.</v>
       </c>
       <c r="D526" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="527">
@@ -7774,7 +7774,7 @@
         <v>I know your name is Antonio, no need to repeat yourself.</v>
       </c>
       <c r="D527" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="528">
@@ -7788,7 +7788,7 @@
         <v xml:space="preserve">Donovan Olson was appointed chairman of the county Board of Supervisors last December. </v>
       </c>
       <c r="D528" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="529">
@@ -7802,7 +7802,7 @@
         <v>I wish to see the actual Mr. Brown.</v>
       </c>
       <c r="D529" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="530">
@@ -7816,7 +7816,7 @@
         <v>The temperatures will be dropping.</v>
       </c>
       <c r="D530" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="531">
@@ -7830,7 +7830,7 @@
         <v>Fieldstone wants to find a workable resolution for the foreclosure problem.</v>
       </c>
       <c r="D531" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="532">
@@ -7858,7 +7858,7 @@
         <v>I have more experience with PCs so I took on the brunt of the load.</v>
       </c>
       <c r="D533" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="534">
@@ -7872,7 +7872,7 @@
         <v>The husband gave her the keys to park the Orshe.</v>
       </c>
       <c r="D534" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="535">
@@ -7886,7 +7886,7 @@
         <v>I can put off these tasks until after class.</v>
       </c>
       <c r="D535" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="536">
@@ -7900,7 +7900,7 @@
         <v>North and south trading regions will not be created.</v>
       </c>
       <c r="D536" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="537">
@@ -7914,7 +7914,7 @@
         <v>The Maxim Hotel needs to be renovated.</v>
       </c>
       <c r="D537" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="538">
@@ -7928,7 +7928,7 @@
         <v>OPEC is worried about the economy.</v>
       </c>
       <c r="D538" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="539">
@@ -7942,7 +7942,7 @@
         <v>The Senate will never get moving on this bill.</v>
       </c>
       <c r="D539" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="540">
@@ -7956,7 +7956,7 @@
         <v>The administration's goal is to create new products and services that meet the needs of consumers.</v>
       </c>
       <c r="D540" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="541">
@@ -7970,7 +7970,7 @@
         <v>They want to make the case for the importance of the war on terror.</v>
       </c>
       <c r="D541" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="542">
@@ -7998,7 +7998,7 @@
         <v>The economic consequences of this war are enormous.</v>
       </c>
       <c r="D543" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="544">
@@ -8012,7 +8012,7 @@
         <v>She didn't want to go to America, but she was afraid to stay in her country.</v>
       </c>
       <c r="D544" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="545">
@@ -8026,7 +8026,7 @@
         <v>You try to figure out what to do.</v>
       </c>
       <c r="D545" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="546">
@@ -8040,7 +8040,7 @@
         <v>The price of freedom is the freedom to do what you want.</v>
       </c>
       <c r="D546" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="547">
@@ -8054,7 +8054,7 @@
         <v>You can do anything you want.</v>
       </c>
       <c r="D547" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="548">
@@ -8068,7 +8068,7 @@
         <v>He wanted to get the information.</v>
       </c>
       <c r="D548" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="549">
@@ -8082,7 +8082,7 @@
         <v>It is a good idea to get the school board to help us.</v>
       </c>
       <c r="D549" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="550">
@@ -8096,7 +8096,7 @@
         <v>The conversation was about the subject of the reporter's interest.</v>
       </c>
       <c r="D550" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="551">
@@ -8110,7 +8110,7 @@
         <v>The novel is about a woman who is not wanted in her own home.</v>
       </c>
       <c r="D551" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="552">
@@ -8124,7 +8124,7 @@
         <v>The school is building a new auditorium.</v>
       </c>
       <c r="D552" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="553">
@@ -8138,7 +8138,7 @@
         <v>The victim does not want to report the crime.</v>
       </c>
       <c r="D553" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="554">
@@ -8152,7 +8152,7 @@
         <v>The government wants to make a system for health care.</v>
       </c>
       <c r="D554" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="555">
@@ -8166,7 +8166,7 @@
         <v>Do we know how to give our children drugs?</v>
       </c>
       <c r="D555" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="556">
@@ -8180,7 +8180,7 @@
         <v>They had the opportunity to do anything they wanted.</v>
       </c>
       <c r="D556" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="557">
@@ -8194,7 +8194,7 @@
         <v>Lawyers have a great opportunity to help the poor.</v>
       </c>
       <c r="D557" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="558">
@@ -8208,7 +8208,7 @@
         <v>The Federal Energy Policy Act of 1992 was repealed in 2005.</v>
       </c>
       <c r="D558" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="559">
@@ -8222,7 +8222,7 @@
         <v>You are here.</v>
       </c>
       <c r="D559" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="560">
@@ -8236,7 +8236,7 @@
         <v>Retail services need contracts.</v>
       </c>
       <c r="D560" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="561">
@@ -8250,7 +8250,7 @@
         <v>Nolte said he never wanted to be a lawyer.</v>
       </c>
       <c r="D561" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="562">
@@ -8264,7 +8264,7 @@
         <v>The state is for sale.</v>
       </c>
       <c r="D562" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="563">
@@ -8278,7 +8278,7 @@
         <v>Scientists want to know what policy makers are doing.</v>
       </c>
       <c r="D563" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="564">
@@ -8292,7 +8292,7 @@
         <v>Stakeholders can be involved in the planning process.</v>
       </c>
       <c r="D564" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="565">
@@ -8306,7 +8306,7 @@
         <v>The change in her mood was due to her friends.</v>
       </c>
       <c r="D565" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="566">
@@ -8320,7 +8320,7 @@
         <v>There is a significant amount of disagreement among the political parties on the need for a single-payer health care system.</v>
       </c>
       <c r="D566" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="567">
@@ -8334,7 +8334,7 @@
         <v>You have a real problem.</v>
       </c>
       <c r="D567" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="568">
@@ -8348,7 +8348,7 @@
         <v>Play a wheel that has 0 and 00 on it.</v>
       </c>
       <c r="D568" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="569">
@@ -8362,7 +8362,7 @@
         <v>I can't tell you what I did.</v>
       </c>
       <c r="D569" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="570">
@@ -8376,7 +8376,7 @@
         <v>The woman doesn't know what she wants.</v>
       </c>
       <c r="D570" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="571">
@@ -8390,7 +8390,7 @@
         <v>He always wants to be right.</v>
       </c>
       <c r="D571" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="572">
@@ -8404,7 +8404,7 @@
         <v>The new program is needed to solve the problem.</v>
       </c>
       <c r="D572" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="573">
@@ -8418,7 +8418,7 @@
         <v>Do you want to stay?</v>
       </c>
       <c r="D573" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="574">
@@ -8432,7 +8432,7 @@
         <v>Police power is needed to make the laws work.</v>
       </c>
       <c r="D574" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="575">
@@ -8446,7 +8446,7 @@
         <v>The government has not done what the people wanted.</v>
       </c>
       <c r="D575" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="576">
@@ -8460,7 +8460,7 @@
         <v>The area will be attracting people who want to come to it.</v>
       </c>
       <c r="D576" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="577">
@@ -8474,7 +8474,7 @@
         <v>He's trying to be rich.</v>
       </c>
       <c r="D577" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="578">
@@ -8488,7 +8488,7 @@
         <v>He was not going to start a war.</v>
       </c>
       <c r="D578" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="579">
@@ -8502,7 +8502,7 @@
         <v>Dr. Livingston did not like him.</v>
       </c>
       <c r="D579" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="580">
@@ -8516,7 +8516,7 @@
         <v>There is a need for a new initiative.</v>
       </c>
       <c r="D580" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="581">
@@ -8530,7 +8530,7 @@
         <v>You need to know the players' names.</v>
       </c>
       <c r="D581" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="582">
@@ -8544,7 +8544,7 @@
         <v>The people need to get a good education.</v>
       </c>
       <c r="D582" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="583">
@@ -8558,7 +8558,7 @@
         <v>We need to consider the costs of other components of the system.</v>
       </c>
       <c r="D583" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="584">
@@ -8572,7 +8572,7 @@
         <v>He has made up his mind about what he wants to do.</v>
       </c>
       <c r="D584" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="585">
@@ -8586,7 +8586,7 @@
         <v>The government needs to do something about the economy.</v>
       </c>
       <c r="D585" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="586">
@@ -8600,7 +8600,7 @@
         <v>He is a very moral person.</v>
       </c>
       <c r="D586" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="587">
@@ -8614,7 +8614,7 @@
         <v>I want to be in charge of the operations.</v>
       </c>
       <c r="D587" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="588">
@@ -8628,7 +8628,7 @@
         <v>The US government wants to allow information to flow freely.</v>
       </c>
       <c r="D588" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="589">
@@ -8642,7 +8642,7 @@
         <v>You do not need a permit to go on the lake.</v>
       </c>
       <c r="D589" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="590">
@@ -8656,7 +8656,7 @@
         <v>There is a need for a comprehensive review of the literature on the topic.</v>
       </c>
       <c r="D590" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="591">
@@ -8670,7 +8670,7 @@
         <v>I don't want to go.</v>
       </c>
       <c r="D591" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="592">
@@ -8684,7 +8684,7 @@
         <v>Diversifying energy supply is important for energy security.</v>
       </c>
       <c r="D592" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="593">
@@ -8698,7 +8698,7 @@
         <v>Miss Paget wanted to say that John was lucky.</v>
       </c>
       <c r="D593" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="594">
@@ -8712,7 +8712,7 @@
         <v>The head of the local school board is in a position to do what he wants to do.</v>
       </c>
       <c r="D594" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="595">
@@ -8726,7 +8726,7 @@
         <v>There needs to be a discussion.</v>
       </c>
       <c r="D595" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="596">
@@ -8740,7 +8740,7 @@
         <v>The Dothraki want to invade the city of Qarth.</v>
       </c>
       <c r="D596" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="597">
@@ -8754,7 +8754,7 @@
         <v>There is something that needs to be done about it.</v>
       </c>
       <c r="D597" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="598">
@@ -8768,7 +8768,7 @@
         <v>The new team is committed to what the coach is trying to do.</v>
       </c>
       <c r="D598" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="599">
@@ -8782,7 +8782,7 @@
         <v>I was more open with her when I was not as nervous.</v>
       </c>
       <c r="D599" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="600">
@@ -8796,7 +8796,7 @@
         <v>Change is needed in the organization.</v>
       </c>
       <c r="D600" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="601">
@@ -8810,7 +8810,7 @@
         <v>The test is not reliable.</v>
       </c>
       <c r="D601" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="602">
@@ -8824,7 +8824,7 @@
         <v>wo more French Canadians came crawling down from the Murray fish-house</v>
       </c>
       <c r="D602" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="603">
@@ -8838,7 +8838,7 @@
         <v>Kissing in public requires consent of a parental figure.</v>
       </c>
       <c r="D603" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="604">
@@ -8852,7 +8852,7 @@
         <v>Andrea von Habsburg is the oldest kid in her family.</v>
       </c>
       <c r="D604" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="605">
@@ -8866,7 +8866,7 @@
         <v>The National park Trust has put up land in over 20 high-priority sites for sale.</v>
       </c>
       <c r="D605" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="606">
@@ -8880,7 +8880,7 @@
         <v>Terrariums must be made from plastic or glass</v>
       </c>
       <c r="D606" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="607">
@@ -8894,7 +8894,7 @@
         <v>The material made to stop erosion on a river bank is not biodegadable</v>
       </c>
       <c r="D607" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="608">
@@ -8908,7 +8908,7 @@
         <v xml:space="preserve">Donald Conroy died at 67 </v>
       </c>
       <c r="D608" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="609">
@@ -8922,7 +8922,7 @@
         <v>In addition to compiling music with the American alternative rock band 10,000 Maniacs, Mary Ramsey should be considered as a member of folk rock duo John &amp; Mary.</v>
       </c>
       <c r="D609" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="610">
@@ -8936,7 +8936,7 @@
         <v>This passage is completed</v>
       </c>
       <c r="D610" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="611">
@@ -8950,7 +8950,7 @@
         <v xml:space="preserve">A valdez requires you to sit upright. </v>
       </c>
       <c r="D611" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="612">
@@ -8964,7 +8964,7 @@
         <v>The speaker is in his second term.</v>
       </c>
       <c r="D612" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="613">
@@ -8978,7 +8978,7 @@
         <v>Janet is an Uncle.</v>
       </c>
       <c r="D613" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="614">
@@ -8992,7 +8992,7 @@
         <v xml:space="preserve">The governor of Abia State is also the president. </v>
       </c>
       <c r="D614" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="615">
@@ -9006,7 +9006,7 @@
         <v>Walter Murray said it was a foolish attack.</v>
       </c>
       <c r="D615" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="616">
@@ -9020,7 +9020,7 @@
         <v xml:space="preserve">Unlimited marine insurance is not available to individuals, only to commercial vessels. </v>
       </c>
       <c r="D616" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="617">
@@ -9034,7 +9034,7 @@
         <v>Constance was not showing interest in the conversation or the subject matter.</v>
       </c>
       <c r="D617" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="618">
@@ -9048,7 +9048,7 @@
         <v>Ibs sufferers should only drink water</v>
       </c>
       <c r="D618" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="619">
@@ -9062,7 +9062,7 @@
         <v>New Day is a 1949 book by Jamaican author V. S. Reid. It is over 46 years old</v>
       </c>
       <c r="D619" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="620">
@@ -9076,7 +9076,7 @@
         <v xml:space="preserve">The vote for the treaty is between 25 and 30 years old. </v>
       </c>
       <c r="D620" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="621">
@@ -9090,7 +9090,7 @@
         <v>The album starts with a D</v>
       </c>
       <c r="D621" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="622">
@@ -9104,7 +9104,7 @@
         <v>Ed Eagan played on the active roster</v>
       </c>
       <c r="D622" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="623">
@@ -9118,7 +9118,7 @@
         <v>Canelo Álvarez vs. Julio César Chávez Jr. was held after 2016</v>
       </c>
       <c r="D623" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="624">
@@ -9132,7 +9132,7 @@
         <v>The hair product isn't cheap.</v>
       </c>
       <c r="D624" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="625">
@@ -9146,7 +9146,7 @@
         <v>Pearse died of natural causes.</v>
       </c>
       <c r="D625" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="626">
@@ -9160,7 +9160,7 @@
         <v>skin cancer correlates to the ozon layer</v>
       </c>
       <c r="D626" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="627">
@@ -9174,7 +9174,7 @@
         <v>Dermal fillers infections may be accompanied by inflammation</v>
       </c>
       <c r="D627" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="628">
@@ -9188,7 +9188,7 @@
         <v>Big Data was a project created by Joywave.</v>
       </c>
       <c r="D628" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="629">
@@ -9202,7 +9202,7 @@
         <v>To treat MSK pain surgically, first rest the muscles.</v>
       </c>
       <c r="D629" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="630">
@@ -9216,7 +9216,7 @@
         <v>surgery contains a g</v>
       </c>
       <c r="D630" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="631">
@@ -9230,7 +9230,7 @@
         <v>surgery is performed by a surgeon</v>
       </c>
       <c r="D631" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="632">
@@ -9244,7 +9244,7 @@
         <v>Most people have not heard of the song Oh My.</v>
       </c>
       <c r="D632" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="633">
@@ -9258,7 +9258,7 @@
         <v>Justice Breyer is a publisher.</v>
       </c>
       <c r="D633" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="634">
@@ -9272,7 +9272,7 @@
         <v>Municipality and comune mean the the same thing.</v>
       </c>
       <c r="D634" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="635">
@@ -9286,7 +9286,7 @@
         <v>Kate Moss has launched her own hair product line.</v>
       </c>
       <c r="D635" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="636">
@@ -9300,7 +9300,7 @@
         <v>The series was about a retired jazz musician named Jackie Evans.</v>
       </c>
       <c r="D636" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="637">
@@ -9314,7 +9314,7 @@
         <v>William Thomas Harris was a Canadian pitcher who batted left-handed for Duguayville</v>
       </c>
       <c r="D637" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="638">
@@ -9328,7 +9328,7 @@
         <v>Sprinkles should be added to the cake.</v>
       </c>
       <c r="D638" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="639">
@@ -9342,7 +9342,7 @@
         <v>Blue Ridge Parkway is in North Carolina and Virginia.</v>
       </c>
       <c r="D639" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="640">
@@ -9356,7 +9356,7 @@
         <v>Gent Funeral Home is responsible for John's death</v>
       </c>
       <c r="D640" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="641">
@@ -9370,7 +9370,7 @@
         <v>The strike will cause delivery delays</v>
       </c>
       <c r="D641" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="642">
@@ -9384,7 +9384,7 @@
         <v>The subcommittee will take 4 trips in the spring of 1999</v>
       </c>
       <c r="D642" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="643">
@@ -9398,7 +9398,7 @@
         <v>Multiply the denominators.</v>
       </c>
       <c r="D643" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="644">
@@ -9412,7 +9412,7 @@
         <v>Someone will do a story about Donald Rickles life.</v>
       </c>
       <c r="D644" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="645">
@@ -9426,7 +9426,7 @@
         <v>Adelphia is not the ninth largest cable service provider in the United States with nearly 5 million subscribers.</v>
       </c>
       <c r="D645" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="646">
@@ -9440,7 +9440,7 @@
         <v>Add the numerators.</v>
       </c>
       <c r="D646" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="647">
@@ -9454,7 +9454,7 @@
         <v>Ilse von Glatz was an advocate in real life</v>
       </c>
       <c r="D647" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="648">
@@ -9468,7 +9468,7 @@
         <v>mcgillis ruling damaged their reputation.</v>
       </c>
       <c r="D648" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="649">
@@ -9482,7 +9482,7 @@
         <v>You should use romaine lettuce for braising.</v>
       </c>
       <c r="D649" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="650">
@@ -9496,7 +9496,7 @@
         <v xml:space="preserve">Dani has helped someone choose differently by volunteering at the suicide prevention hotline. </v>
       </c>
       <c r="D650" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="651">
@@ -9510,7 +9510,7 @@
         <v>College Football all-star game players play in the East-West Shrine Game.</v>
       </c>
       <c r="D651" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="652">
@@ -9524,7 +9524,7 @@
         <v>Thomas Ryan was 52 years old in 2008.</v>
       </c>
       <c r="D652" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="653">
@@ -9538,7 +9538,7 @@
         <v>Dani knew how hard it could be.</v>
       </c>
       <c r="D653" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="654">
@@ -9552,7 +9552,7 @@
         <v>Authorities did not came to the conclusion that it was a murder</v>
       </c>
       <c r="D654" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="655">
@@ -9566,7 +9566,7 @@
         <v>Henry died 7 years after inventing the machine.</v>
       </c>
       <c r="D655" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="656">
@@ -9580,7 +9580,7 @@
         <v>Selma Diamond died at age 60</v>
       </c>
       <c r="D656" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="657">
@@ -9594,7 +9594,7 @@
         <v>My home province is Sasquatch.</v>
       </c>
       <c r="D657" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="658">
@@ -9608,7 +9608,7 @@
         <v>Russia listens to America.</v>
       </c>
       <c r="D658" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="659">
@@ -9622,7 +9622,7 @@
         <v xml:space="preserve">Steven Chealander works for the National Transportation Safety Board. </v>
       </c>
       <c r="D659" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="660">
@@ -9636,7 +9636,7 @@
         <v>The all star game is played after the postseason of college football.</v>
       </c>
       <c r="D660" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="661">
@@ -9650,7 +9650,7 @@
         <v>The education system is deeply flawed and no child should be left behind.</v>
       </c>
       <c r="D661" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="662">
@@ -9664,7 +9664,7 @@
         <v>Baby Boomers are the ones to blame for the sky rocket house prices.</v>
       </c>
       <c r="D662" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="663">
@@ -9678,7 +9678,7 @@
         <v>Hank got a filling two days ago</v>
       </c>
       <c r="D663" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="664">
@@ -9692,7 +9692,7 @@
         <v>The Tampa team picked Erickson in the 4th round of the 1991 selection process.</v>
       </c>
       <c r="D664" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="665">
@@ -9706,7 +9706,7 @@
         <v>Witta son of Wecta like to listen to the lute.</v>
       </c>
       <c r="D665" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="666">
@@ -9720,7 +9720,7 @@
         <v>The water main break could have been avoided.</v>
       </c>
       <c r="D666" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="667">
@@ -9734,7 +9734,7 @@
         <v>All five friends are female.</v>
       </c>
       <c r="D667" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="668">
@@ -9748,7 +9748,7 @@
         <v>Kota Ramakrishna Karanth was born after April</v>
       </c>
       <c r="D668" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="669">
@@ -9762,7 +9762,7 @@
         <v>My colleague also mentioned we could accept some of the proposed changes that were borderline good.</v>
       </c>
       <c r="D669" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="670">
@@ -9776,7 +9776,7 @@
         <v>The Blue Ridge Parkway has been sold to private parties.</v>
       </c>
       <c r="D670" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="671">
@@ -9790,7 +9790,7 @@
         <v>The speaker know's the color of Sara's eyes</v>
       </c>
       <c r="D671" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="672">
@@ -9804,7 +9804,7 @@
         <v>Private parties are interested in buying land from the National Park Trust.</v>
       </c>
       <c r="D672" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="673">
@@ -9818,7 +9818,7 @@
         <v>Manson will not play a 74th game</v>
       </c>
       <c r="D673" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="674">
@@ -9832,7 +9832,7 @@
         <v>ABC ran Lost for at least 6 seasons</v>
       </c>
       <c r="D674" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="675">
@@ -9846,7 +9846,7 @@
         <v>trigger foods are essential to be aware of and to avoid of both ibs and gerd since same condtions</v>
       </c>
       <c r="D675" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="676">
@@ -9860,7 +9860,7 @@
         <v>Ira Heiden's first film role was in 1987.</v>
       </c>
       <c r="D676" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="677">
@@ -9874,7 +9874,7 @@
         <v xml:space="preserve">Realtor's in Florida cannot act with misconduct but can be ineffective when representing their clients. </v>
       </c>
       <c r="D677" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="678">
@@ -9888,7 +9888,7 @@
         <v>The science advisory board is being audited</v>
       </c>
       <c r="D678" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="679">
@@ -9902,7 +9902,7 @@
         <v>Worms get infected by dog feces.</v>
       </c>
       <c r="D679" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="680">
@@ -9916,7 +9916,7 @@
         <v>Rahul Gandhi really digs Narendra Modi.</v>
       </c>
       <c r="D680" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="681">
@@ -9930,7 +9930,7 @@
         <v>The Cooper–Frost–Austin House offers private tours in early May.</v>
       </c>
       <c r="D681" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="682">
@@ -9944,7 +9944,7 @@
         <v xml:space="preserve">She arrived at mid-forenoon. </v>
       </c>
       <c r="D682" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="683">
@@ -9958,7 +9958,7 @@
         <v>The Axis of Perdition are a korean pop group</v>
       </c>
       <c r="D683" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="684">
@@ -9972,7 +9972,7 @@
         <v>Archbishops should be treated just like any other member of the church</v>
       </c>
       <c r="D684" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="685">
@@ -9986,7 +9986,7 @@
         <v>Ratatouille could be played in the car</v>
       </c>
       <c r="D685" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="686">
@@ -10000,7 +10000,7 @@
         <v>They were scared when they came back all the kids would be sick.</v>
       </c>
       <c r="D686" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="687">
@@ -10014,7 +10014,7 @@
         <v>A poem must have rhymes.</v>
       </c>
       <c r="D687" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="688">
@@ -10028,7 +10028,7 @@
         <v>Ethan could have grown the herbs in the same garden.</v>
       </c>
       <c r="D688" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="689">
@@ -10042,7 +10042,7 @@
         <v>The Associated Press copywrote this announcement.</v>
       </c>
       <c r="D689" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="690">
@@ -10056,7 +10056,7 @@
         <v>Orson Welles was a producer.</v>
       </c>
       <c r="D690" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="691">
@@ -10070,7 +10070,7 @@
         <v>Joey Graceffa is a computer engineer.</v>
       </c>
       <c r="D691" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="692">
@@ -10084,7 +10084,7 @@
         <v>Radiohead has three albums released.</v>
       </c>
       <c r="D692" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="693">
@@ -10098,7 +10098,7 @@
         <v>Venom is usually connected to Spiderman.</v>
       </c>
       <c r="D693" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="694">
@@ -10112,7 +10112,7 @@
         <v>Marilyn Burns was an fencer.</v>
       </c>
       <c r="D694" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="695">
@@ -10126,7 +10126,7 @@
         <v>Jim Henson was a singer.</v>
       </c>
       <c r="D695" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="696">
@@ -10140,7 +10140,7 @@
         <v>Karan Johar is a president.</v>
       </c>
       <c r="D696" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="697">
@@ -10154,7 +10154,7 @@
         <v>Orson Welles was a thespian.</v>
       </c>
       <c r="D697" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="698">
@@ -10168,7 +10168,7 @@
         <v>Clint Eastwood performs music.</v>
       </c>
       <c r="D698" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="699">
@@ -10182,7 +10182,7 @@
         <v>Queen Victoria was queen of a country.</v>
       </c>
       <c r="D699" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="700">
@@ -10196,7 +10196,7 @@
         <v>Warm Leatherette is by a woman.</v>
       </c>
       <c r="D700" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="701">
@@ -10210,7 +10210,7 @@
         <v>X-Men: Days of Future Past came out after 2010.</v>
       </c>
       <c r="D701" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="702">
@@ -10224,7 +10224,7 @@
         <v>Jordan Knight is a film actor.</v>
       </c>
       <c r="D702" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="703">
@@ -10238,7 +10238,7 @@
         <v>Minnesota is in France.</v>
       </c>
       <c r="D703" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="704">
@@ -10252,7 +10252,7 @@
         <v>Huntington's disease is a disorder that may be inherited.</v>
       </c>
       <c r="D704" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="705">
@@ -10266,7 +10266,7 @@
         <v>Sue Sylvester is portrayed exclusively by a male actor.</v>
       </c>
       <c r="D705" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="706">
@@ -10280,7 +10280,7 @@
         <v>Joan Crawford began her career as an actress.</v>
       </c>
       <c r="D706" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="707">
@@ -10294,7 +10294,7 @@
         <v>Leonardo da Vinci is dating one of the greatest painters of all time.</v>
       </c>
       <c r="D707" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="708">
@@ -10308,7 +10308,7 @@
         <v>Fred Trump was thirteen years old in December, 1918.</v>
       </c>
       <c r="D708" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="709">
@@ -10322,7 +10322,7 @@
         <v>Sofia Coppola is a sparkling wine.</v>
       </c>
       <c r="D709" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="710">
@@ -10336,7 +10336,7 @@
         <v>X-Men (film) has a cast that is an American actor, and singer name Ian Mckellen.</v>
       </c>
       <c r="D710" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="711">
@@ -10350,7 +10350,7 @@
         <v>Newcastle United F.C.'s most successful period ended in May of 1910.</v>
       </c>
       <c r="D711" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="712">
@@ -10364,7 +10364,7 @@
         <v>Leonardo da Vinci studied anatomy.</v>
       </c>
       <c r="D712" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="713">
@@ -10378,7 +10378,7 @@
         <v>Joey Graceffa is from a republic made up of a federation, based on a constitution.</v>
       </c>
       <c r="D713" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="714">
@@ -10392,7 +10392,7 @@
         <v>Glee is a horror comedy.</v>
       </c>
       <c r="D714" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="715">
@@ -10406,7 +10406,7 @@
         <v>The director of the pilot episode of The Blacklist was born during the Kennedy administration.</v>
       </c>
       <c r="D715" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="716">
@@ -10420,7 +10420,7 @@
         <v>Roman Reigns is a gardener.</v>
       </c>
       <c r="D716" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="717">
@@ -10434,7 +10434,7 @@
         <v>Ted Kennedy is a United States senator.</v>
       </c>
       <c r="D717" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="718">
@@ -10448,7 +10448,7 @@
         <v>Supernatural is a series.</v>
       </c>
       <c r="D718" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="719">
@@ -10462,7 +10462,7 @@
         <v>The Twelfth Doctor is in a British television show.</v>
       </c>
       <c r="D719" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="720">
@@ -10476,7 +10476,7 @@
         <v>Jack Paar died on a date in the 21st century.</v>
       </c>
       <c r="D720" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="721">
@@ -10490,7 +10490,7 @@
         <v>Planet of the Apes shot sequences in and around the Statue of Liberty.</v>
       </c>
       <c r="D721" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="722">
@@ -10504,7 +10504,7 @@
         <v>One More Light was released through CBS.</v>
       </c>
       <c r="D722" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="723">
@@ -10518,7 +10518,7 @@
         <v>Wentworth is a single episode on television.</v>
       </c>
       <c r="D723" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="724">
@@ -10532,7 +10532,7 @@
         <v>Robert Browning was a foremost Russian Empire-era poet.</v>
       </c>
       <c r="D724" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="725">
@@ -10546,7 +10546,7 @@
         <v>Audrey Horne was introduced in Twin Peaks: The Return.</v>
       </c>
       <c r="D725" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="726">
@@ -10560,7 +10560,7 @@
         <v>Avatar: The Last Airbender's main character was Aang.</v>
       </c>
       <c r="D726" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="727">
@@ -10574,7 +10574,7 @@
         <v>Evan Goldberg is a German director.</v>
       </c>
       <c r="D727" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="728">
@@ -10588,7 +10588,7 @@
         <v>Cindy McCain is American.</v>
       </c>
       <c r="D728" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="729">
@@ -10602,7 +10602,7 @@
         <v>Coldplay is a British band.</v>
       </c>
       <c r="D729" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="730">
@@ -10616,7 +10616,7 @@
         <v>Tim Allen starred in an American show.</v>
       </c>
       <c r="D730" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="731">
@@ -10630,7 +10630,7 @@
         <v>Tony Blair was leader of the Conservative Party.</v>
       </c>
       <c r="D731" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="732">
@@ -10644,7 +10644,7 @@
         <v>Heather Watson is a champion.</v>
       </c>
       <c r="D732" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="733">
@@ -10658,7 +10658,7 @@
         <v>John McCain is known for his work to restore diplomatic relations with Russia.</v>
       </c>
       <c r="D733" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="734">
@@ -10672,7 +10672,7 @@
         <v>Vladimir Putin was the Chairman of a government.</v>
       </c>
       <c r="D734" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="735">
@@ -10686,7 +10686,7 @@
         <v>The Guest stars American film actors.</v>
       </c>
       <c r="D735" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="736">
@@ -10700,7 +10700,7 @@
         <v>Timothy Olyphant was an animal.</v>
       </c>
       <c r="D736" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="737">
@@ -10714,7 +10714,7 @@
         <v>Frank Sinatra's middle name was Sam.</v>
       </c>
       <c r="D737" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="738">
@@ -10728,7 +10728,7 @@
         <v>Sage Stallone was a father.</v>
       </c>
       <c r="D738" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="739">
@@ -10742,7 +10742,7 @@
         <v>Mao Zedong was Russian.</v>
       </c>
       <c r="D739" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="740">
@@ -10756,7 +10756,7 @@
         <v>Lee Harvey Oswald assassinated the 35th President of the United States.</v>
       </c>
       <c r="D740" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="741">
@@ -10770,7 +10770,7 @@
         <v>Gabourey Sidibe is a citizen of the United States.</v>
       </c>
       <c r="D741" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="742">
@@ -10784,7 +10784,7 @@
         <v>Glee was a fim.</v>
       </c>
       <c r="D742" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="743">
@@ -10798,7 +10798,7 @@
         <v>Tony Blair is an actor.</v>
       </c>
       <c r="D743" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="744">
@@ -10812,7 +10812,7 @@
         <v>Anderson Cooper is a person.</v>
       </c>
       <c r="D744" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="745">
@@ -10826,7 +10826,7 @@
         <v>Heather Watson is a mother.</v>
       </c>
       <c r="D745" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="746">
@@ -10840,7 +10840,7 @@
         <v>George Clooney is a cartoonist.</v>
       </c>
       <c r="D746" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="747">
@@ -10854,7 +10854,7 @@
         <v>Avril Lavigne is a musician.</v>
       </c>
       <c r="D747" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="748">
@@ -10868,7 +10868,7 @@
         <v>Emilio Estevez was born in a manger.</v>
       </c>
       <c r="D748" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="749">
@@ -10882,7 +10882,7 @@
         <v>Miranda Kerr was a Canadian Victoria's Secret model.</v>
       </c>
       <c r="D749" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="750">
@@ -10896,7 +10896,7 @@
         <v>Hulk is a creation.</v>
       </c>
       <c r="D750" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="751">
@@ -10910,7 +10910,7 @@
         <v>Monica Seles played tennis.</v>
       </c>
       <c r="D751" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="752">
@@ -10924,7 +10924,7 @@
         <v>Penny Dreadful started in the 21st century.</v>
       </c>
       <c r="D752" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="753">
@@ -10938,7 +10938,7 @@
         <v>Doug Jones is employed in the cinema business.</v>
       </c>
       <c r="D753" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="754">
@@ -10952,7 +10952,7 @@
         <v>Warm Leatherette is by a Jamaican-born singer and it was released in 1980.</v>
       </c>
       <c r="D754" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="755">
@@ -10966,7 +10966,7 @@
         <v>Glee was a TV series.</v>
       </c>
       <c r="D755" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="756">
@@ -10980,7 +10980,7 @@
         <v>Estella Warren is a Gemini.</v>
       </c>
       <c r="D756" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="757">
@@ -10994,7 +10994,7 @@
         <v>Desperate Housewives is a tv series.</v>
       </c>
       <c r="D757" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="758">
@@ -11008,7 +11008,7 @@
         <v>Eminem was a Gemini.</v>
       </c>
       <c r="D758" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="759">
@@ -11022,7 +11022,7 @@
         <v>Thomas DeSimone disappeared in Haiti.</v>
       </c>
       <c r="D759" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="760">
@@ -11036,7 +11036,7 @@
         <v>William R. Tolbert Jr. was killed.</v>
       </c>
       <c r="D760" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="761">
@@ -11050,7 +11050,7 @@
         <v>Miranda Cosgrove is a race car driver</v>
       </c>
       <c r="D761" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="762">
@@ -11064,7 +11064,7 @@
         <v>Wynonna Judd is involved in water aerobics.</v>
       </c>
       <c r="D762" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="763">
@@ -11078,7 +11078,7 @@
         <v>Tré Cool is the drummer for Green Day.</v>
       </c>
       <c r="D763" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="764">
@@ -11092,7 +11092,7 @@
         <v>David Schwimmer finished acting in Friends on October 8, 2004.</v>
       </c>
       <c r="D764" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="765">
@@ -11106,7 +11106,7 @@
         <v>Gennady Golovkin is a fencer.</v>
       </c>
       <c r="D765" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="766">
@@ -11120,7 +11120,7 @@
         <v>Dennis Hopper was a person.</v>
       </c>
       <c r="D766" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="767">
@@ -11134,7 +11134,7 @@
         <v>Sage Stallone was born in China.</v>
       </c>
       <c r="D767" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="768">
@@ -11148,7 +11148,7 @@
         <v>Laurence Olivier was in America.</v>
       </c>
       <c r="D768" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="769">
@@ -11162,7 +11162,7 @@
         <v>Gennady Golovkin is a squid.</v>
       </c>
       <c r="D769" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="770">
@@ -11176,7 +11176,7 @@
         <v>Novak Djokovic is an athlete.</v>
       </c>
       <c r="D770" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="771">
@@ -11190,7 +11190,7 @@
         <v>Grace Jones performed in A View to Kill.</v>
       </c>
       <c r="D771" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="772">
@@ -11204,7 +11204,7 @@
         <v>Dennis Hopper was an Australian.</v>
       </c>
       <c r="D772" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="773">
@@ -11218,7 +11218,7 @@
         <v>Love &amp; Friendship is a commercial.</v>
       </c>
       <c r="D773" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="774">
@@ -11232,7 +11232,7 @@
         <v>Spain is a country.</v>
       </c>
       <c r="D774" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="775">
@@ -11246,7 +11246,7 @@
         <v>Tony Goldwyn is a German producer.</v>
       </c>
       <c r="D775" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="776">
@@ -11260,7 +11260,7 @@
         <v>Roman Reigns is a professional baseball player.</v>
       </c>
       <c r="D776" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="777">
@@ -11274,7 +11274,7 @@
         <v>Vladimir Putin was President from 1997 to 2008.</v>
       </c>
       <c r="D777" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="778">
@@ -11288,7 +11288,7 @@
         <v>Seattle is the largest person in the state of Washington.</v>
       </c>
       <c r="D778" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="779">
@@ -11302,7 +11302,7 @@
         <v>Andy Kaufman was a savage.</v>
       </c>
       <c r="D779" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="780">
@@ -11316,7 +11316,7 @@
         <v>Danny Carey has no middle name.</v>
       </c>
       <c r="D780" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="781">
@@ -11330,7 +11330,7 @@
         <v>Tiger Woods won the Palm Springs Invitational.</v>
       </c>
       <c r="D781" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="782">
@@ -11344,7 +11344,7 @@
         <v>BRIT School was founded in 1922.</v>
       </c>
       <c r="D782" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="783">
@@ -11358,7 +11358,7 @@
         <v>John Wayne Gacy Jr. was involved in crime.</v>
       </c>
       <c r="D783" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="784">
@@ -11372,7 +11372,7 @@
         <v>The commander of the Schutzstaffel was Heinrich Himmler.</v>
       </c>
       <c r="D784" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="785">
@@ -11386,7 +11386,7 @@
         <v>Fergie has a dog called "Outspoken".</v>
       </c>
       <c r="D785" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="786">
@@ -11400,7 +11400,7 @@
         <v>Joey Graceffa worked with a website headquartered in San Burno, California.</v>
       </c>
       <c r="D786" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="787">
@@ -11414,7 +11414,7 @@
         <v>The Leftovers stars an actor.</v>
       </c>
       <c r="D787" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="788">
@@ -11428,7 +11428,7 @@
         <v>Carmelo Anthony plays for a football team.</v>
       </c>
       <c r="D788" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="789">
@@ -11442,7 +11442,7 @@
         <v>Tom Felton is a Gemini.</v>
       </c>
       <c r="D789" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="790">
@@ -11456,7 +11456,7 @@
         <v>Glee's last season was ordered on April 19, 2013.</v>
       </c>
       <c r="D790" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="791">
@@ -11470,7 +11470,7 @@
         <v>Glee was a fim.</v>
       </c>
       <c r="D791" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="792">
@@ -11484,7 +11484,7 @@
         <v>All laws regarding People's right to child custody mandate parents must be married.</v>
       </c>
       <c r="D792" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="793">
@@ -11498,7 +11498,7 @@
         <v>A trial had witnesses on the stand</v>
       </c>
       <c r="D793" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="794">
@@ -11512,7 +11512,7 @@
         <v>Dexter laughed at the idea of "I have a dream" ice cream.</v>
       </c>
       <c r="D794" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="795">
@@ -11526,7 +11526,7 @@
         <v>Fish admitted he might be wrong.</v>
       </c>
       <c r="D795" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="796">
@@ -11540,7 +11540,7 @@
         <v>Not to play devil's advocate but, Mussolini was the main inspiration for Tudjman, since he was a young politician.</v>
       </c>
       <c r="D796" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="797">
@@ -11554,7 +11554,7 @@
         <v>Falwell-style Christians believe Christ was Jewish</v>
       </c>
       <c r="D797" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="798">
@@ -11568,7 +11568,7 @@
         <v>They say his information is not worth considering.</v>
       </c>
       <c r="D798" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="799">
@@ -11582,7 +11582,7 @@
         <v>Richey and the doctor denied having committed any wrongful acts against Wynette during the trial.</v>
       </c>
       <c r="D799" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="800">
@@ -11596,7 +11596,7 @@
         <v>The reader kept reading the book to the end.</v>
       </c>
       <c r="D800" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="801">
@@ -11610,7 +11610,7 @@
         <v>Several convicted felons will be allowed to interact closely with the unguarded president and special interest groups.</v>
       </c>
       <c r="D801" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="802">
@@ -11624,7 +11624,7 @@
         <v>The New Yorker halted the Letters from Europr column.</v>
       </c>
       <c r="D802" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="803">
@@ -11638,7 +11638,7 @@
         <v>My name could possibly be Pierre LeCluck.</v>
       </c>
       <c r="D803" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="804">
@@ -11652,7 +11652,7 @@
         <v>Pinball machines could be used for gambling.</v>
       </c>
       <c r="D804" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="805">
@@ -11666,7 +11666,7 @@
         <v>A crime committed involving a bomb will be prosecuted like any other crime.</v>
       </c>
       <c r="D805" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="806">
@@ -11680,7 +11680,7 @@
         <v>New Hampshire and Iowa often change one's thoughts.</v>
       </c>
       <c r="D806" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="807">
@@ -11694,7 +11694,7 @@
         <v>There is a genius alive right now who can help us with this.</v>
       </c>
       <c r="D807" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="808">
@@ -11708,7 +11708,7 @@
         <v>No question about it there is life on other planets.</v>
       </c>
       <c r="D808" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="809">
@@ -11722,7 +11722,7 @@
         <v>Dorthey Healyey knew Morris.</v>
       </c>
       <c r="D809" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="810">
@@ -11736,7 +11736,7 @@
         <v>It is wrong to appeal to that position.</v>
       </c>
       <c r="D810" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="811">
@@ -11750,7 +11750,7 @@
         <v>Lobbyists and large doners have easier access to Senators</v>
       </c>
       <c r="D811" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="812">
@@ -11764,7 +11764,7 @@
         <v>There were actually more nations in 1992 that could have participated,</v>
       </c>
       <c r="D812" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="813">
@@ -11778,7 +11778,7 @@
         <v>Someone probably slipped Kenneth Starr a tape of this week's This Week.</v>
       </c>
       <c r="D813" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="814">
@@ -11792,7 +11792,7 @@
         <v>Reebok intentionally gave the she a provocative name.</v>
       </c>
       <c r="D814" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="815">
@@ -11806,7 +11806,7 @@
         <v>The adopted child bullies everyone on the playground.</v>
       </c>
       <c r="D815" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="816">
@@ -11820,7 +11820,7 @@
         <v>Catastrophic shutdowns of electrical grids, banks, air-traffic computers, medical equipment, and the like will now be avoided for years.</v>
       </c>
       <c r="D816" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="817">
@@ -11834,7 +11834,7 @@
         <v>The hypotheses that Lang believes are majorly confirmed are false.</v>
       </c>
       <c r="D817" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="818">
@@ -11848,7 +11848,7 @@
         <v>Today, a spy claimed that to the dead man's knowledge, when interviewed by a letter writer, that the U.S. authorities might have approved Diem's assassination.</v>
       </c>
       <c r="D818" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="819">
@@ -11876,7 +11876,7 @@
         <v>You could see the pain written all over his face and he looked miserable.</v>
       </c>
       <c r="D820" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="821">
@@ -11890,7 +11890,7 @@
         <v>She had a secret from them.</v>
       </c>
       <c r="D821" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="822">
@@ -11904,7 +11904,7 @@
         <v>It was difficult to tell if they were in the correct place.</v>
       </c>
       <c r="D822" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="823">
@@ -11918,7 +11918,7 @@
         <v>The friends of deregulation have been given many gifts in past anniversaries.</v>
       </c>
       <c r="D823" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="824">
@@ -11932,7 +11932,7 @@
         <v>Amman was a costly failure</v>
       </c>
       <c r="D824" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="825">
@@ -11946,7 +11946,7 @@
         <v>Employers should sell eggs to stockholders.</v>
       </c>
       <c r="D825" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="826">
@@ -11960,7 +11960,7 @@
         <v>College students could care less about sweatshops.</v>
       </c>
       <c r="D826" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="827">
@@ -11974,7 +11974,7 @@
         <v>It is possible that congress will overspend.</v>
       </c>
       <c r="D827" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="828">
@@ -11988,7 +11988,7 @@
         <v>Jess Gupta may be gay.</v>
       </c>
       <c r="D828" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="829">
@@ -12002,7 +12002,7 @@
         <v>Henry liked to make a girl squeal with happiness by giving her things that she likes.</v>
       </c>
       <c r="D829" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="830">
@@ -12016,7 +12016,7 @@
         <v>The Mormons practiced polygamy.</v>
       </c>
       <c r="D830" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="831">
@@ -12030,7 +12030,7 @@
         <v>Investors should  pull their money out of Microsoft due to the negative information.</v>
       </c>
       <c r="D831" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="832">
@@ -12044,7 +12044,7 @@
         <v>They thought he should be spending more time online.</v>
       </c>
       <c r="D832" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="833">
@@ -12072,7 +12072,7 @@
         <v>The person isn't thinking about their decisions.</v>
       </c>
       <c r="D834" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="835">
@@ -12086,7 +12086,7 @@
         <v>The author has seen Merchant of Venice</v>
       </c>
       <c r="D835" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="836">
@@ -12100,7 +12100,7 @@
         <v>The product should hit stores by the summer months of June, July, and August.</v>
       </c>
       <c r="D836" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="837">
@@ -12114,7 +12114,7 @@
         <v>Society may collapse one day.</v>
       </c>
       <c r="D837" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="838">
@@ -12128,7 +12128,7 @@
         <v>It's likely the author will get a fatal disease long before death.</v>
       </c>
       <c r="D838" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="839">
@@ -12142,7 +12142,7 @@
         <v>We have access to copyrighted material</v>
       </c>
       <c r="D839" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="840">
@@ -12156,7 +12156,7 @@
         <v>They might have all been slaves</v>
       </c>
       <c r="D840" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="841">
@@ -12170,7 +12170,7 @@
         <v>The United States and Russia are in a war together.</v>
       </c>
       <c r="D841" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="842">
@@ -12184,7 +12184,7 @@
         <v>There is little added protection from joining NATO.</v>
       </c>
       <c r="D842" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="843">
@@ -12198,7 +12198,7 @@
         <v>Equity options are rarely legitimate for the consumer.</v>
       </c>
       <c r="D843" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="844">
@@ -12212,7 +12212,7 @@
         <v>The program will expand to inculde police.</v>
       </c>
       <c r="D844" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="845">
@@ -12226,7 +12226,7 @@
         <v>He doesn't judge people to harshly who have different religious ideas than his own.</v>
       </c>
       <c r="D845" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="846">
@@ -12240,7 +12240,7 @@
         <v>They have choices for getting out of the predicament.</v>
       </c>
       <c r="D846" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="847">
@@ -12254,7 +12254,7 @@
         <v>She has already changed</v>
       </c>
       <c r="D847" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="848">
@@ -12268,7 +12268,7 @@
         <v>The loans that were big would make the difference.</v>
       </c>
       <c r="D848" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="849">
@@ -12282,7 +12282,7 @@
         <v>Apple gave permission to a few companies, such as IBM and HP, to produce hardware running their operating system.</v>
       </c>
       <c r="D849" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="850">
@@ -12296,7 +12296,7 @@
         <v>It could be possible to ask people to leave without having family issues.</v>
       </c>
       <c r="D850" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="851">
@@ -12310,7 +12310,7 @@
         <v>Intelligence has many explanations and possibilities, including odd.</v>
       </c>
       <c r="D851" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="852">
@@ -12324,7 +12324,7 @@
         <v>Iraqi commando units may have a hard time escaping any reports from the news media.</v>
       </c>
       <c r="D852" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="853">
@@ -12338,7 +12338,7 @@
         <v>High ranking employees of a shoe company are not being looked into.</v>
       </c>
       <c r="D853" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="854">
@@ -12352,7 +12352,7 @@
         <v>Tripp actually rode a dragon but the media ignored that and focused on her testimony in court instead.</v>
       </c>
       <c r="D854" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="855">
@@ -12380,7 +12380,7 @@
         <v xml:space="preserve">The book ends with the argument </v>
       </c>
       <c r="D856" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="857">
@@ -12394,7 +12394,7 @@
         <v xml:space="preserve">It is imperative that non-profit providers of human services use foreign practices and mindsets in order to work. </v>
       </c>
       <c r="D857" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="858">
@@ -12408,7 +12408,7 @@
         <v>The retained frequent flyer miles may be redeemed for cash value.</v>
       </c>
       <c r="D858" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="859">
@@ -12422,7 +12422,7 @@
         <v>He will almost definitely end up being traded</v>
       </c>
       <c r="D859" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="860">
@@ -12436,7 +12436,7 @@
         <v>Certain types of proposed service innovations should be considered by the USPS.</v>
       </c>
       <c r="D860" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="861">
@@ -12450,7 +12450,7 @@
         <v xml:space="preserve">Microsoft has engaged in questionable behavior and is being probed. </v>
       </c>
       <c r="D861" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="862">
@@ -12464,7 +12464,7 @@
         <v xml:space="preserve"> Bill Bradley and Al Gore are the only others to be affected by Net voting fraud besides the Arizona Democrats.</v>
       </c>
       <c r="D862" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="863">
@@ -12478,7 +12478,7 @@
         <v>Stock options are a good idea.</v>
       </c>
       <c r="D863" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="864">
@@ -12492,7 +12492,7 @@
         <v>Nobody is sure what a bravura is, but doctors are hopeful it can be removed.</v>
       </c>
       <c r="D864" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="865">
@@ -12506,7 +12506,7 @@
         <v>A looks like a country pub with a cobblestone courtyard.</v>
       </c>
       <c r="D865" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="866">
@@ -12520,7 +12520,7 @@
         <v>The National Academy of Sciences reported on research proirities for PM.</v>
       </c>
       <c r="D866" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="867">
@@ -12534,7 +12534,7 @@
         <v>It's not unusual for tour guides to sneak into the Portugese government's official residence.</v>
       </c>
       <c r="D867" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="868">
@@ -12548,7 +12548,7 @@
         <v>Greece could absorb the islands of the northern and eastern Italy and took this opportunity.</v>
       </c>
       <c r="D868" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="869">
@@ -12562,7 +12562,7 @@
         <v>The severe time constraints on the Year 2000 conversion efforts should have absolutely no effect on the confidentiality of sensitive data.</v>
       </c>
       <c r="D869" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="870">
@@ -12576,7 +12576,7 @@
         <v>He only talked about the president in private.</v>
       </c>
       <c r="D870" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="871">
@@ -12590,7 +12590,7 @@
         <v>You are the true Franklin, no matter how I am dressed.</v>
       </c>
       <c r="D871" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="872">
@@ -12604,7 +12604,7 @@
         <v>The trees looked wonderful.</v>
       </c>
       <c r="D872" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="873">
@@ -12618,7 +12618,7 @@
         <v>The Republicans used to be interested in keeping Gingrich around.</v>
       </c>
       <c r="D873" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="874">
@@ -12632,7 +12632,7 @@
         <v>Someone must know where it is.</v>
       </c>
       <c r="D874" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="875">
@@ -12646,7 +12646,7 @@
         <v>I think they sent a letter to my husband to find out if your husband works for TI.</v>
       </c>
       <c r="D875" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="876">
@@ -12660,7 +12660,7 @@
         <v>How many servings does that make?</v>
       </c>
       <c r="D876" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="877">
@@ -12674,7 +12674,7 @@
         <v>They have no knowledge of the fashion sense.</v>
       </c>
       <c r="D877" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="878">
@@ -12688,7 +12688,7 @@
         <v>Drew knew Don Quixote.</v>
       </c>
       <c r="D878" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="879">
@@ -12702,7 +12702,7 @@
         <v>NASA's supporters have always maintained that it was a funding issue.</v>
       </c>
       <c r="D879" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="880">
@@ -12716,7 +12716,7 @@
         <v>Drew accepted an offer for the horse.</v>
       </c>
       <c r="D880" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="881">
@@ -12730,7 +12730,7 @@
         <v>You should.</v>
       </c>
       <c r="D881" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="882">
@@ -12744,7 +12744,7 @@
         <v>they very well could be</v>
       </c>
       <c r="D882" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="883">
@@ -12758,7 +12758,7 @@
         <v>It's worth having extra because it might not get voted.</v>
       </c>
       <c r="D883" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="884">
@@ -12772,7 +12772,7 @@
         <v>It is estimated that the trial will cost Scheck from $1000,000 to $300,000, which she could easily afford.</v>
       </c>
       <c r="D884" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="885">
@@ -12786,7 +12786,7 @@
         <v xml:space="preserve">San'doro picked up Jon so he could stand. </v>
       </c>
       <c r="D885" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="886">
@@ -12800,7 +12800,7 @@
         <v>One wonders if his history of being a circus clown effected his photography.</v>
       </c>
       <c r="D886" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="887">
@@ -12814,7 +12814,7 @@
         <v>The decision will set whether these estimates may change or not.</v>
       </c>
       <c r="D887" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="888">
@@ -12828,7 +12828,7 @@
         <v>The ruling elite dictate the national economy.</v>
       </c>
       <c r="D888" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="889">
@@ -12842,7 +12842,7 @@
         <v>It was very suspicious that she made a new will on the day that she died.</v>
       </c>
       <c r="D889" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="890">
@@ -12856,7 +12856,7 @@
         <v xml:space="preserve">Contractor should be involved </v>
       </c>
       <c r="D890" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="891">
@@ -12870,7 +12870,7 @@
         <v>A person may have no preference between two offers.</v>
       </c>
       <c r="D891" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="892">
@@ -12884,7 +12884,7 @@
         <v xml:space="preserve">The new emissions rule was published in May of 1996. </v>
       </c>
       <c r="D892" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="893">
@@ -12898,7 +12898,7 @@
         <v>It may not end up as a democracy.</v>
       </c>
       <c r="D893" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="894">
@@ -12912,7 +12912,7 @@
         <v xml:space="preserve">The value is large and there must be a sort of error. </v>
       </c>
       <c r="D894" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="895">
@@ -12926,7 +12926,7 @@
         <v xml:space="preserve">You must have died in the war. </v>
       </c>
       <c r="D895" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="896">
@@ -12940,7 +12940,7 @@
         <v>The author is happy that the idea did not come to fruition.</v>
       </c>
       <c r="D896" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="897">
@@ -12954,7 +12954,7 @@
         <v>Advanced intake systems must be installed to assist more clients.</v>
       </c>
       <c r="D897" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="898">
@@ -12968,7 +12968,7 @@
         <v>The federal fiscal policy may affect national saving in many ways.</v>
       </c>
       <c r="D898" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="899">
@@ -12982,7 +12982,7 @@
         <v>The banana cream pie was the greatest and can be taken home.</v>
       </c>
       <c r="D899" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="900">
@@ -12996,7 +12996,7 @@
         <v xml:space="preserve">Albert could be heard walking on the floor above. </v>
       </c>
       <c r="D900" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="901">
@@ -13010,7 +13010,7 @@
         <v>The candle light made the man appear even more robust.</v>
       </c>
       <c r="D901" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="902">
@@ -13024,7 +13024,7 @@
         <v>The concord is within NAFTA regs.</v>
       </c>
       <c r="D902" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="903">
@@ -13038,7 +13038,7 @@
         <v xml:space="preserve"> The best way to conduct an email marketing campaign is just to wing it. Make a list of customers. Bugging people is a great way to get a following. Email marketing originated in the nineteen eighties</v>
       </c>
       <c r="D903" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="904">
@@ -13052,7 +13052,7 @@
         <v>There are no members from New York</v>
       </c>
       <c r="D904" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="905">
@@ -13066,7 +13066,7 @@
         <v>The puppy was for being a year older</v>
       </c>
       <c r="D905" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="906">
@@ -13080,7 +13080,7 @@
         <v xml:space="preserve">YouTube user Streetcap1 posted a series of pictures taken from Chinese lunar rover Change'e 4. </v>
       </c>
       <c r="D906" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="907">
@@ -13094,7 +13094,7 @@
         <v>The state of being distracted can be perceived through visual senses.</v>
       </c>
       <c r="D907" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="908">
@@ -13108,7 +13108,7 @@
         <v>Rye St Antony School does not allow 9 year old boys.</v>
       </c>
       <c r="D908" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="909">
@@ -13122,7 +13122,7 @@
         <v>The governor has proposed twice as much nation building.</v>
       </c>
       <c r="D909" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="910">
@@ -13136,7 +13136,7 @@
         <v>There are at least less than ten people killed.</v>
       </c>
       <c r="D910" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="911">
@@ -13150,7 +13150,7 @@
         <v>Fall color is not dependant on rainfall.</v>
       </c>
       <c r="D911" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="912">
@@ -13164,7 +13164,7 @@
         <v xml:space="preserve">Jusuf Kalla is not the Philippine President </v>
       </c>
       <c r="D912" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="913">
@@ -13178,7 +13178,7 @@
         <v>Shared zones take urban design into account.</v>
       </c>
       <c r="D913" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="914">
@@ -13192,7 +13192,7 @@
         <v>From Madison it takes less than 5 hours to drive to.</v>
       </c>
       <c r="D914" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="915">
@@ -13206,7 +13206,7 @@
         <v>Hell Blade charted higher than Time's End.</v>
       </c>
       <c r="D915" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="916">
@@ -13220,7 +13220,7 @@
         <v>The doctor was just going for a walk when all this took place.</v>
       </c>
       <c r="D916" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="917">
@@ -13234,7 +13234,7 @@
         <v>Chuck Wright was one of many background singers for Quiet Riot.</v>
       </c>
       <c r="D917" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="918">
@@ -13248,7 +13248,7 @@
         <v>The central hall cannot hold more than 10,014 people for basketball games.</v>
       </c>
       <c r="D918" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="919">
@@ -13262,7 +13262,7 @@
         <v>A few constitutional lawyers would be examined</v>
       </c>
       <c r="D919" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="920">
@@ -13276,7 +13276,7 @@
         <v>weak cardboard is better than sturdy</v>
       </c>
       <c r="D920" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="921">
@@ -13290,7 +13290,7 @@
         <v>Some medical values are big.</v>
       </c>
       <c r="D921" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="922">
@@ -13304,7 +13304,7 @@
         <v>Eric thought Neil looked better in work clothes rather than dress clothes.</v>
       </c>
       <c r="D922" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="923">
@@ -13318,7 +13318,7 @@
         <v>Jobs are being lost in America under the president</v>
       </c>
       <c r="D923" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="924">
@@ -13332,7 +13332,7 @@
         <v xml:space="preserve">Economic growth is the most important focus for the Commander in Chief of the Land of the Free and the Home of the Brave. </v>
       </c>
       <c r="D924" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="925">
@@ -13346,7 +13346,7 @@
         <v>"Wherein an affidavit is provided" is very specific language.</v>
       </c>
       <c r="D925" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="926">
@@ -13360,7 +13360,7 @@
         <v>Mr. Weasel is a fictional character.</v>
       </c>
       <c r="D926" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="927">
@@ -13374,7 +13374,7 @@
         <v>The men were shot at from inside a building they were walking past.</v>
       </c>
       <c r="D927" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="928">
@@ -13388,7 +13388,7 @@
         <v>The man did not die on scene</v>
       </c>
       <c r="D928" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="929">
@@ -13402,7 +13402,7 @@
         <v>A slow breathing pattern is breathing in twice and dreaming of a vacation.</v>
       </c>
       <c r="D929" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="930">
@@ -13416,7 +13416,7 @@
         <v>The president believes in having strong relations with Europe.</v>
       </c>
       <c r="D930" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="931">
@@ -13430,7 +13430,7 @@
         <v>All for Love was written by less than four people</v>
       </c>
       <c r="D931" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="932">
@@ -13444,7 +13444,7 @@
         <v>From Madison it takes less than 6 hours to drive to.</v>
       </c>
       <c r="D932" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="933">
@@ -13458,7 +13458,7 @@
         <v>Bridge grammar is not smaller than island grammar.</v>
       </c>
       <c r="D933" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="934">
@@ -13472,7 +13472,7 @@
         <v>This show is no longer called "Jack Horkheimer: Star Hustler"</v>
       </c>
       <c r="D934" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="935">
@@ -13486,7 +13486,7 @@
         <v>Bubblegum is better for blowing bubbles.</v>
       </c>
       <c r="D935" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="936">
@@ -13500,7 +13500,7 @@
         <v>This speaker has attended many Royal Assents.</v>
       </c>
       <c r="D936" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="937">
@@ -13514,7 +13514,7 @@
         <v>for one years the Canadian government has been engaged in secret negotiations</v>
       </c>
       <c r="D937" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="938">
@@ -13528,7 +13528,7 @@
         <v>Gore is addressed as governor.</v>
       </c>
       <c r="D938" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="939">
@@ -13542,7 +13542,7 @@
         <v>Streetcap1 was on the moon when he posted photos from the Chinese lunar rover Change'e 3.</v>
       </c>
       <c r="D939" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="940">
@@ -13556,7 +13556,7 @@
         <v>Change’e 3 did not post clips to Youtube.</v>
       </c>
       <c r="D940" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="941">
@@ -13570,7 +13570,7 @@
         <v>Trends are coming back.</v>
       </c>
       <c r="D941" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="942">
@@ -13584,7 +13584,7 @@
         <v>their were sidewalks in the framers mind.</v>
       </c>
       <c r="D942" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="943">
@@ -13598,7 +13598,7 @@
         <v>While Zdeno Chara is the tallest NHL player, Mike Cvik is not one of the taller players.</v>
       </c>
       <c r="D943" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="944">
@@ -13612,7 +13612,7 @@
         <v>Holding Back the River reached higher in the charts than the band's debut album.</v>
       </c>
       <c r="D944" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="945">
@@ -13626,7 +13626,7 @@
         <v>Gordon hit more than once in another game this season</v>
       </c>
       <c r="D945" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="946">
@@ -13640,7 +13640,7 @@
         <v>Beat TV was broadcast for more than two hours at a time.</v>
       </c>
       <c r="D946" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="947">
@@ -13654,7 +13654,7 @@
         <v>There are more than 10 schools in the Big 12 Conference.</v>
       </c>
       <c r="D947" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="948">
@@ -13668,7 +13668,7 @@
         <v>Glasgow's Kelvingrove Museum was in India</v>
       </c>
       <c r="D948" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="949">
@@ -13682,7 +13682,7 @@
         <v>Annet Artani didn't write all of her songs</v>
       </c>
       <c r="D949" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="950">
@@ -13696,7 +13696,7 @@
         <v>Amy and Anna met up again after they met by chance at the cafe</v>
       </c>
       <c r="D950" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="951">
@@ -13710,7 +13710,7 @@
         <v>Bob Adams Field is twenty five miles east of Yampa Valley Regional Airport.</v>
       </c>
       <c r="D951" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="952">
@@ -13724,7 +13724,7 @@
         <v>Everyone does not deserve medicare</v>
       </c>
       <c r="D952" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="953">
@@ -13738,7 +13738,7 @@
         <v>Neil Gordon is not a snappy dresser.</v>
       </c>
       <c r="D953" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="954">
@@ -13752,7 +13752,7 @@
         <v>Statement contains less than about 28 words</v>
       </c>
       <c r="D954" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="955">
@@ -13766,7 +13766,7 @@
         <v>Everyone talked for durations of time within 5 minutes of the next person.</v>
       </c>
       <c r="D955" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="956">
@@ -13780,7 +13780,7 @@
         <v>Nancy Hart Douglas was not a scout under General Stonewall Jackson.</v>
       </c>
       <c r="D956" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="957">
@@ -13794,7 +13794,7 @@
         <v>Thailand and Cambodia can't reach an agreement on the ownership of a temple.</v>
       </c>
       <c r="D957" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="958">
@@ -13808,7 +13808,7 @@
         <v>More than three weeks after Pamela's murder, Lois Riess was in police custody.</v>
       </c>
       <c r="D958" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="959">
@@ -13822,7 +13822,7 @@
         <v>Sodium Saccharin has an o</v>
       </c>
       <c r="D959" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="960">
@@ -13836,7 +13836,7 @@
         <v>Jensen Ackles is not known for his roles in television as Jason Teague in Smallville.</v>
       </c>
       <c r="D960" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="961">
@@ -13850,7 +13850,7 @@
         <v>Cheaper by the dozen was directed by a cat.</v>
       </c>
       <c r="D961" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="962">
@@ -13864,7 +13864,7 @@
         <v>The Coen brothers directed a thriller film.</v>
       </c>
       <c r="D962" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="963">
@@ -13878,7 +13878,7 @@
         <v>Muhammad was a prophet.</v>
       </c>
       <c r="D963" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="964">
@@ -13892,7 +13892,7 @@
         <v>Venus Williams plays singles in tennis.</v>
       </c>
       <c r="D964" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="965">
@@ -13906,7 +13906,7 @@
         <v>Brittany Murphy starred in a movie.</v>
       </c>
       <c r="D965" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="966">
@@ -13920,7 +13920,7 @@
         <v>Bermuda was colonized in 1609.</v>
       </c>
       <c r="D966" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="967">
@@ -13934,7 +13934,7 @@
         <v>Harry Styles and his bandmates released the folk album Midnight Memories.</v>
       </c>
       <c r="D967" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="968">
@@ -13948,7 +13948,7 @@
         <v>Fantastic Beasts and Where to Find Them is a nature book.</v>
       </c>
       <c r="D968" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="969">
@@ -13962,7 +13962,7 @@
         <v>Mirka Federer is a tennis player who played professionally and plays no longer.</v>
       </c>
       <c r="D969" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="970">
@@ -13976,7 +13976,7 @@
         <v>Big Show's birth name is Paul Donald Wight II, although he uses Big Show for professional wrestling.</v>
       </c>
       <c r="D970" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="971">
@@ -13990,7 +13990,7 @@
         <v>Leslie Uggams appeared in a film directed by Tim Miller.</v>
       </c>
       <c r="D971" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="972">
@@ -14004,7 +14004,7 @@
         <v>Venus Williams plays singles in tennis.</v>
       </c>
       <c r="D972" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="973">
@@ -14018,7 +14018,7 @@
         <v>Drew Barrymore starred in a film.</v>
       </c>
       <c r="D973" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="974">
@@ -14032,7 +14032,7 @@
         <v>Toy Story was not based upon previously published material allowing it to be nominated for Best Original Screenplay.</v>
       </c>
       <c r="D974" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="975">
@@ -14046,7 +14046,7 @@
         <v>Malala Yousafzai is an advocate for women's right to education.</v>
       </c>
       <c r="D975" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="976">
@@ -14060,7 +14060,7 @@
         <v>Pi is a number.</v>
       </c>
       <c r="D976" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="977">
@@ -14074,7 +14074,7 @@
         <v>A high percentage of people in Azerbaijan are literate.</v>
       </c>
       <c r="D977" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="978">
@@ -14088,7 +14088,7 @@
         <v>Italy is has a longer official title.</v>
       </c>
       <c r="D978" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="979">
@@ -14102,7 +14102,7 @@
         <v>Matt Groening won Primetime Emmys for The Simpsons.</v>
       </c>
       <c r="D979" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="980">
@@ -14116,7 +14116,7 @@
         <v>Muhammad is significant to religion.</v>
       </c>
       <c r="D980" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="981">
@@ -14130,7 +14130,7 @@
         <v>John McEnroe was a tennis player.</v>
       </c>
       <c r="D981" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="982">
@@ -14144,7 +14144,7 @@
         <v>Black Mirror is a racehorse.</v>
       </c>
       <c r="D982" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="983">
@@ -14158,7 +14158,7 @@
         <v>Catching Fire is a genre.</v>
       </c>
       <c r="D983" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="984">
@@ -14172,7 +14172,7 @@
         <v>John McCain was accused of corruption in 1989 as part of the Keating Five.</v>
       </c>
       <c r="D984" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="985">
@@ -14186,7 +14186,7 @@
         <v>Valerian and the City of a Thousand Planets features an actor.</v>
       </c>
       <c r="D985" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="986">
@@ -14200,7 +14200,7 @@
         <v>Venus Williams plays singles in tennis.</v>
       </c>
       <c r="D986" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="987">
@@ -14214,7 +14214,7 @@
         <v>Margaret of Valois had sisters.</v>
       </c>
       <c r="D987" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="988">
@@ -14228,7 +14228,7 @@
         <v>Matt Groening won ten Italian beef sandwiches for The Simpsons.</v>
       </c>
       <c r="D988" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="989">
@@ -14242,7 +14242,7 @@
         <v>The Nashville Songwriters Association International provides music industry education.</v>
       </c>
       <c r="D989" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="990">
@@ -14256,7 +14256,7 @@
         <v>Batman Begins predated North American independence.</v>
       </c>
       <c r="D990" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="991">
@@ -14270,7 +14270,7 @@
         <v>Toy Story was not based upon previously published material allowing it to be nominated for Best Original Screenplay.</v>
       </c>
       <c r="D991" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="992">
@@ -14284,7 +14284,7 @@
         <v>Billy Joel is in the performing arts industry.</v>
       </c>
       <c r="D992" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="993">
@@ -14298,7 +14298,7 @@
         <v>Catching Fire was released in paperback.</v>
       </c>
       <c r="D993" t="str">
-        <v>NonSense</v>
+        <v>Neutral</v>
       </c>
     </row>
     <row r="994">
@@ -14312,7 +14312,7 @@
         <v>Brittany Murphy acted.</v>
       </c>
       <c r="D994" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="995">
@@ -14326,7 +14326,7 @@
         <v>Foo Fighters make music.</v>
       </c>
       <c r="D995" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="996">
@@ -14340,7 +14340,7 @@
         <v>The Boeing 777 is the world's farthest-range airliner.</v>
       </c>
       <c r="D996" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="997">
@@ -14354,7 +14354,7 @@
         <v>Muhammad is significant to religion.</v>
       </c>
       <c r="D997" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="998">
@@ -14368,7 +14368,7 @@
         <v>Transformers: Revenge of the Fallen is a film.</v>
       </c>
       <c r="D998" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="999">
@@ -14382,7 +14382,7 @@
         <v>Big Show's stage name is Paul Donald Wight II.</v>
       </c>
       <c r="D999" t="str">
-        <v>NonSense</v>
+        <v>Contradiction</v>
       </c>
     </row>
     <row r="1000">
@@ -14396,7 +14396,7 @@
         <v>Muhammad is significant to religion.</v>
       </c>
       <c r="D1000" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
     <row r="1001">
@@ -14410,7 +14410,7 @@
         <v>Joaquin Phoenix has directed films.</v>
       </c>
       <c r="D1001" t="str">
-        <v>NonSense</v>
+        <v>Entailment</v>
       </c>
     </row>
   </sheetData>
